--- a/fact_evaluacion_proveedores/outputs/06_historial_entrenamiento.xlsx
+++ b/fact_evaluacion_proveedores/outputs/06_historial_entrenamiento.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -723,7 +723,7 @@
         <v>0.9245793345635487</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9153769359402071</v>
+        <v>0.9153769359402069</v>
       </c>
       <c r="D18" t="n">
         <v>0.7757390417940877</v>
@@ -791,7 +791,7 @@
         <v>0.8832698042071591</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8745684310580748</v>
+        <v>0.874568431058075</v>
       </c>
       <c r="D22" t="n">
         <v>0.7769622833843017</v>
@@ -876,7 +876,7 @@
         <v>0.8351143389578034</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8269162253008595</v>
+        <v>0.8269162253008594</v>
       </c>
       <c r="D27" t="n">
         <v>0.7779816513761468</v>
@@ -907,7 +907,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8169060710677069</v>
+        <v>0.8169060710677067</v>
       </c>
       <c r="C29" t="n">
         <v>0.8088880470405844</v>
@@ -995,7 +995,7 @@
         <v>0.7740201606405389</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7664136197644068</v>
+        <v>0.7664136197644067</v>
       </c>
       <c r="D34" t="n">
         <v>0.7871559633027523</v>
@@ -1012,7 +1012,7 @@
         <v>0.7658932897727747</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7583622356342277</v>
+        <v>0.7583622356342276</v>
       </c>
       <c r="D35" t="n">
         <v>0.7887869520897044</v>
@@ -1026,7 +1026,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.7579150244470456</v>
+        <v>0.7579150244470455</v>
       </c>
       <c r="C36" t="n">
         <v>0.7504569678311082</v>
@@ -1077,7 +1077,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.7348590058411041</v>
+        <v>0.734859005841104</v>
       </c>
       <c r="C39" t="n">
         <v>0.7276038681198048</v>
@@ -1148,7 +1148,7 @@
         <v>0.7060995385594645</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6990740503989542</v>
+        <v>0.6990740503989541</v>
       </c>
       <c r="D43" t="n">
         <v>0.801630988786952</v>
@@ -1165,7 +1165,7 @@
         <v>0.6992482081778352</v>
       </c>
       <c r="C44" t="n">
-        <v>0.6922724662204585</v>
+        <v>0.6922724662204583</v>
       </c>
       <c r="D44" t="n">
         <v>0.8026503567787971</v>
@@ -1230,7 +1230,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.673114684094191</v>
+        <v>0.6731146840941908</v>
       </c>
       <c r="C48" t="n">
         <v>0.6663073403069032</v>
@@ -1284,7 +1284,7 @@
         <v>0.6547669418727285</v>
       </c>
       <c r="C51" t="n">
-        <v>0.6480552676875609</v>
+        <v>0.6480552676875608</v>
       </c>
       <c r="D51" t="n">
         <v>0.8061162079510703</v>
@@ -1488,7 +1488,7 @@
         <v>0.5904630575129579</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5839277995908384</v>
+        <v>0.5839277995908383</v>
       </c>
       <c r="D63" t="n">
         <v>0.8161060142711519</v>
@@ -1539,7 +1539,7 @@
         <v>0.57631440173897</v>
       </c>
       <c r="C66" t="n">
-        <v>0.5697868113854676</v>
+        <v>0.5697868113854675</v>
       </c>
       <c r="D66" t="n">
         <v>0.819367991845056</v>
@@ -1553,7 +1553,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>0.5717463939046987</v>
+        <v>0.5717463939046986</v>
       </c>
       <c r="C67" t="n">
         <v>0.565219203534014</v>
@@ -1604,7 +1604,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>0.5584619820794474</v>
+        <v>0.5584619820794475</v>
       </c>
       <c r="C70" t="n">
         <v>0.5519306472626907</v>
@@ -1723,7 +1723,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>0.5297126925394476</v>
+        <v>0.5297126925394477</v>
       </c>
       <c r="C77" t="n">
         <v>0.5231485410879214</v>
@@ -1879,7 +1879,7 @@
         <v>0.4967751487825189</v>
       </c>
       <c r="C86" t="n">
-        <v>0.4901397973278601</v>
+        <v>0.4901397973278603</v>
       </c>
       <c r="D86" t="n">
         <v>0.8391437308868501</v>
@@ -1947,7 +1947,7 @@
         <v>0.4833983298907558</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4767246250832057</v>
+        <v>0.4767246250832056</v>
       </c>
       <c r="D90" t="n">
         <v>0.8464831804281345</v>
@@ -1964,7 +1964,7 @@
         <v>0.4801641334356632</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4734803099030863</v>
+        <v>0.4734803099030864</v>
       </c>
       <c r="D91" t="n">
         <v>0.8487257900101937</v>
@@ -1978,7 +1978,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>0.4769721388223459</v>
+        <v>0.4769721388223461</v>
       </c>
       <c r="C92" t="n">
         <v>0.4702779934162908</v>
@@ -2015,7 +2015,7 @@
         <v>0.470711283355915</v>
       </c>
       <c r="C94" t="n">
-        <v>0.4639958954908044</v>
+        <v>0.4639958954908045</v>
       </c>
       <c r="D94" t="n">
         <v>0.85361875637105</v>
@@ -2083,7 +2083,7 @@
         <v>0.4586586660918754</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4518984375768811</v>
+        <v>0.4518984375768812</v>
       </c>
       <c r="D98" t="n">
         <v>0.8576962283384302</v>
@@ -2165,7 +2165,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>0.4444070361100054</v>
+        <v>0.4444070361100051</v>
       </c>
       <c r="C103" t="n">
         <v>0.4375863492632938</v>
@@ -2202,7 +2202,7 @@
         <v>0.4389405297496087</v>
       </c>
       <c r="C105" t="n">
-        <v>0.4320942700750845</v>
+        <v>0.4320942700750846</v>
       </c>
       <c r="D105" t="n">
         <v>0.8648318042813455</v>
@@ -2267,7 +2267,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>0.4283784576270366</v>
+        <v>0.4283784576270365</v>
       </c>
       <c r="C109" t="n">
         <v>0.4214786201067499</v>
@@ -2301,7 +2301,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>0.4232725614515724</v>
+        <v>0.4232725614515723</v>
       </c>
       <c r="C111" t="n">
         <v>0.4163446990337523</v>
@@ -2321,7 +2321,7 @@
         <v>0.4207612506318312</v>
       </c>
       <c r="C112" t="n">
-        <v>0.4138190624657204</v>
+        <v>0.4138190624657203</v>
       </c>
       <c r="D112" t="n">
         <v>0.8713557594291539</v>
@@ -2471,7 +2471,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>0.399308203391136</v>
+        <v>0.3993082033911361</v>
       </c>
       <c r="C121" t="n">
         <v>0.3922274793610618</v>
@@ -2559,7 +2559,7 @@
         <v>0.3881957991019874</v>
       </c>
       <c r="C126" t="n">
-        <v>0.3810304615190109</v>
+        <v>0.3810304615190108</v>
       </c>
       <c r="D126" t="n">
         <v>0.8841997961264016</v>
@@ -2576,7 +2576,7 @@
         <v>0.3860356759216588</v>
       </c>
       <c r="C127" t="n">
-        <v>0.3788527462434918</v>
+        <v>0.3788527462434919</v>
       </c>
       <c r="D127" t="n">
         <v>0.8864424057084608</v>
@@ -2590,7 +2590,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>0.3838954074303573</v>
+        <v>0.3838954074303574</v>
       </c>
       <c r="C128" t="n">
         <v>0.3766946606589806</v>
@@ -2641,7 +2641,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>0.377590025884507</v>
+        <v>0.3775900258845071</v>
       </c>
       <c r="C131" t="n">
         <v>0.3703344706991573</v>
@@ -2726,7 +2726,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>0.3674451908350882</v>
+        <v>0.3674451908350883</v>
       </c>
       <c r="C136" t="n">
         <v>0.360093728285085</v>
@@ -2743,7 +2743,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>0.3654679820352451</v>
+        <v>0.3654679820352452</v>
       </c>
       <c r="C137" t="n">
         <v>0.3580966497813787</v>
@@ -2794,10 +2794,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>0.3596346657635976</v>
+        <v>0.3596346657635977</v>
       </c>
       <c r="C140" t="n">
-        <v>0.3522023430413847</v>
+        <v>0.3522023430413848</v>
       </c>
       <c r="D140" t="n">
         <v>0.891335372069317</v>
@@ -2862,7 +2862,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>0.3520765718971847</v>
+        <v>0.3520765718971848</v>
       </c>
       <c r="C144" t="n">
         <v>0.3445597052841003</v>
@@ -2882,7 +2882,7 @@
         <v>0.3502246585322267</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3426860818148624</v>
+        <v>0.3426860818148625</v>
       </c>
       <c r="D145" t="n">
         <v>0.8929663608562691</v>
@@ -2950,7 +2950,7 @@
         <v>0.3429608574589579</v>
       </c>
       <c r="C149" t="n">
-        <v>0.335333160363576</v>
+        <v>0.3353331603635761</v>
       </c>
       <c r="D149" t="n">
         <v>0.8937818552497452</v>
@@ -2981,10 +2981,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>0.3394124610232118</v>
+        <v>0.3394124610232117</v>
       </c>
       <c r="C151" t="n">
-        <v>0.3317388482966787</v>
+        <v>0.3317388482966788</v>
       </c>
       <c r="D151" t="n">
         <v>0.8941896024464832</v>
@@ -2998,7 +2998,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>0.3376584819931893</v>
+        <v>0.3376584819931894</v>
       </c>
       <c r="C152" t="n">
         <v>0.3299615766671524</v>
@@ -3032,7 +3032,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>0.3341900917001154</v>
+        <v>0.3341900917001155</v>
       </c>
       <c r="C154" t="n">
         <v>0.326445939023798</v>
@@ -3066,7 +3066,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>0.3307733628199127</v>
+        <v>0.3307733628199128</v>
       </c>
       <c r="C156" t="n">
         <v>0.3229810915362312</v>
@@ -3100,7 +3100,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>0.3274070541248355</v>
+        <v>0.3274070541248356</v>
       </c>
       <c r="C158" t="n">
         <v>0.31956580902673</v>
@@ -3273,7 +3273,7 @@
         <v>0.3112935809196949</v>
       </c>
       <c r="C168" t="n">
-        <v>0.3031953726583301</v>
+        <v>0.3031953726583302</v>
       </c>
       <c r="D168" t="n">
         <v>0.9080530071355759</v>
@@ -3307,7 +3307,7 @@
         <v>0.3082077638234317</v>
       </c>
       <c r="C170" t="n">
-        <v>0.3000559250545461</v>
+        <v>0.3000559250545462</v>
       </c>
       <c r="D170" t="n">
         <v>0.909072375127421</v>
@@ -3372,7 +3372,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>0.3021663055406188</v>
+        <v>0.3021663055406189</v>
       </c>
       <c r="C174" t="n">
         <v>0.2939052166912853</v>
@@ -3528,7 +3528,7 @@
         <v>0.2891820289908675</v>
       </c>
       <c r="C183" t="n">
-        <v>0.2806668050765369</v>
+        <v>0.280666805076537</v>
       </c>
       <c r="D183" t="n">
         <v>0.9141692150866463</v>
@@ -3576,7 +3576,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>0.2850338307743112</v>
+        <v>0.2850338307743113</v>
       </c>
       <c r="C186" t="n">
         <v>0.2764318317371794</v>
@@ -3664,7 +3664,7 @@
         <v>0.2783121971783706</v>
       </c>
       <c r="C191" t="n">
-        <v>0.2695639178939709</v>
+        <v>0.269563917893971</v>
       </c>
       <c r="D191" t="n">
         <v>0.9176350662589194</v>
@@ -3746,7 +3746,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>0.2718238387491929</v>
+        <v>0.271823838749193</v>
       </c>
       <c r="C196" t="n">
         <v>0.2629278548570202</v>
@@ -3919,7 +3919,7 @@
         <v>0.2595181516526365</v>
       </c>
       <c r="C206" t="n">
-        <v>0.2503255341524772</v>
+        <v>0.2503255341524773</v>
       </c>
       <c r="D206" t="n">
         <v>0.9259938837920489</v>
@@ -3936,7 +3936,7 @@
         <v>0.2583351954024594</v>
       </c>
       <c r="C207" t="n">
-        <v>0.2491130039386283</v>
+        <v>0.2491130039386284</v>
       </c>
       <c r="D207" t="n">
         <v>0.926197757390418</v>
@@ -3950,10 +3950,10 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>0.2571606855728451</v>
+        <v>0.2571606855728452</v>
       </c>
       <c r="C208" t="n">
-        <v>0.2479089605179986</v>
+        <v>0.2479089605179987</v>
       </c>
       <c r="D208" t="n">
         <v>0.926809378185525</v>
@@ -4103,10 +4103,10 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>0.2469617481378789</v>
+        <v>0.246961748137879</v>
       </c>
       <c r="C217" t="n">
-        <v>0.2374469968284784</v>
+        <v>0.2374469968284785</v>
       </c>
       <c r="D217" t="n">
         <v>0.9290519877675841</v>
@@ -4140,7 +4140,7 @@
         <v>0.2447839414243742</v>
       </c>
       <c r="C219" t="n">
-        <v>0.2352116657861484</v>
+        <v>0.2352116657861485</v>
       </c>
       <c r="D219" t="n">
         <v>0.9302752293577982</v>
@@ -4188,7 +4188,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>0.2415759050551978</v>
+        <v>0.2415759050551979</v>
       </c>
       <c r="C222" t="n">
         <v>0.2319181617906964</v>
@@ -4225,7 +4225,7 @@
         <v>0.239475750590029</v>
       </c>
       <c r="C224" t="n">
-        <v>0.2297616335537977</v>
+        <v>0.2297616335537978</v>
       </c>
       <c r="D224" t="n">
         <v>0.9314984709480122</v>
@@ -4290,7 +4290,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>0.235366148154921</v>
+        <v>0.2353661481549212</v>
       </c>
       <c r="C228" t="n">
         <v>0.2255409068730455</v>
@@ -4497,7 +4497,7 @@
         <v>0.2237346641287083</v>
       </c>
       <c r="C240" t="n">
-        <v>0.2135914852814875</v>
+        <v>0.2135914852814876</v>
       </c>
       <c r="D240" t="n">
         <v>0.9372069317023446</v>
@@ -4582,7 +4582,7 @@
         <v>0.2191823862988291</v>
       </c>
       <c r="C245" t="n">
-        <v>0.2089146465861422</v>
+        <v>0.2089146465861423</v>
       </c>
       <c r="D245" t="n">
         <v>0.9398572884811417</v>
@@ -4599,7 +4599,7 @@
         <v>0.2182918228399034</v>
       </c>
       <c r="C246" t="n">
-        <v>0.2079997838103455</v>
+        <v>0.2079997838103456</v>
       </c>
       <c r="D246" t="n">
         <v>0.9398572884811417</v>
@@ -4718,7 +4718,7 @@
         <v>0.2122377180636861</v>
       </c>
       <c r="C253" t="n">
-        <v>0.2017815848317878</v>
+        <v>0.2017815848317879</v>
       </c>
       <c r="D253" t="n">
         <v>0.944546381243629</v>
@@ -4749,7 +4749,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>0.2105643527306774</v>
+        <v>0.2105643527306775</v>
       </c>
       <c r="C255" t="n">
         <v>0.2000633215748528</v>
@@ -4837,7 +4837,7 @@
         <v>0.2064867212980184</v>
       </c>
       <c r="C260" t="n">
-        <v>0.1958774310819531</v>
+        <v>0.1958774310819532</v>
       </c>
       <c r="D260" t="n">
         <v>0.9498470948012232</v>
@@ -4851,7 +4851,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>0.205688956918066</v>
+        <v>0.2056889569180661</v>
       </c>
       <c r="C261" t="n">
         <v>0.1950587072909345</v>
@@ -4868,7 +4868,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="n">
-        <v>0.2048970054871185</v>
+        <v>0.2048970054871186</v>
       </c>
       <c r="C262" t="n">
         <v>0.1942460294135865</v>
@@ -4902,7 +4902,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="n">
-        <v>0.2033303584235159</v>
+        <v>0.203330358423516</v>
       </c>
       <c r="C264" t="n">
         <v>0.1926386312414291</v>
@@ -4970,7 +4970,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="n">
-        <v>0.20026481651139</v>
+        <v>0.2002648165113901</v>
       </c>
       <c r="C268" t="n">
         <v>0.1894944096464874</v>
@@ -4990,7 +4990,7 @@
         <v>0.199512283543467</v>
       </c>
       <c r="C269" t="n">
-        <v>0.1887227970265992</v>
+        <v>0.1887227970265991</v>
       </c>
       <c r="D269" t="n">
         <v>0.9514780835881753</v>
@@ -5058,7 +5058,7 @@
         <v>0.1965562283012747</v>
       </c>
       <c r="C273" t="n">
-        <v>0.1856927893245926</v>
+        <v>0.1856927893245927</v>
       </c>
       <c r="D273" t="n">
         <v>0.9537206931702344</v>
@@ -5310,7 +5310,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="n">
-        <v>0.1862006581556866</v>
+        <v>0.1862006581556867</v>
       </c>
       <c r="C288" t="n">
         <v>0.1750933888682749</v>
@@ -5463,10 +5463,10 @@
         <v>296</v>
       </c>
       <c r="B297" t="n">
-        <v>0.1804986247680145</v>
+        <v>0.1804986247680146</v>
       </c>
       <c r="C297" t="n">
-        <v>0.1692697978325694</v>
+        <v>0.1692697978325695</v>
       </c>
       <c r="D297" t="n">
         <v>0.9561671763506626</v>
@@ -5480,7 +5480,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>0.1798870920952528</v>
+        <v>0.1798870920952529</v>
       </c>
       <c r="C298" t="n">
         <v>0.1686458642814015</v>
@@ -5582,7 +5582,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="n">
-        <v>0.176306219388028</v>
+        <v>0.1763062193880279</v>
       </c>
       <c r="C304" t="n">
         <v>0.1649950942382191</v>
@@ -5650,7 +5650,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="n">
-        <v>0.1740004472225428</v>
+        <v>0.1740004472225429</v>
       </c>
       <c r="C308" t="n">
         <v>0.1626469204172679</v>
@@ -5769,7 +5769,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>0.1701146029781461</v>
+        <v>0.1701146029781462</v>
       </c>
       <c r="C315" t="n">
         <v>0.1586946486933297</v>
@@ -5837,7 +5837,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="n">
-        <v>0.1679757459698358</v>
+        <v>0.1679757459698357</v>
       </c>
       <c r="C319" t="n">
         <v>0.156522117129164</v>
@@ -5888,7 +5888,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>0.1664089891065134</v>
+        <v>0.1664089891065135</v>
       </c>
       <c r="C322" t="n">
         <v>0.1549320766705978</v>
@@ -5939,10 +5939,10 @@
         <v>324</v>
       </c>
       <c r="B325" t="n">
-        <v>0.1648733496712275</v>
+        <v>0.1648733496712274</v>
       </c>
       <c r="C325" t="n">
-        <v>0.1533747995068025</v>
+        <v>0.1533747995068024</v>
       </c>
       <c r="D325" t="n">
         <v>0.9592252803261978</v>
@@ -5973,7 +5973,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="n">
-        <v>0.1638664759506497</v>
+        <v>0.1638664759506498</v>
       </c>
       <c r="C327" t="n">
         <v>0.1523543951111566</v>
@@ -6061,7 +6061,7 @@
         <v>0.1614066855567223</v>
       </c>
       <c r="C332" t="n">
-        <v>0.1498638219014112</v>
+        <v>0.1498638219014113</v>
       </c>
       <c r="D332" t="n">
         <v>0.9598369011213048</v>
@@ -6129,7 +6129,7 @@
         <v>0.1594960158774651</v>
       </c>
       <c r="C336" t="n">
-        <v>0.1479315592765046</v>
+        <v>0.1479315592765045</v>
       </c>
       <c r="D336" t="n">
         <v>0.9600407747196738</v>
@@ -6231,7 +6231,7 @@
         <v>0.1567211917698214</v>
       </c>
       <c r="C342" t="n">
-        <v>0.1451291825181876</v>
+        <v>0.1451291825181875</v>
       </c>
       <c r="D342" t="n">
         <v>0.9606523955147809</v>
@@ -6245,7 +6245,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="n">
-        <v>0.1562690215707448</v>
+        <v>0.1562690215707447</v>
       </c>
       <c r="C343" t="n">
         <v>0.1446729660856154</v>
@@ -6282,7 +6282,7 @@
         <v>0.155373280756111</v>
       </c>
       <c r="C345" t="n">
-        <v>0.1437695879847431</v>
+        <v>0.1437695879847432</v>
       </c>
       <c r="D345" t="n">
         <v>0.9608562691131498</v>
@@ -6296,7 +6296,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="n">
-        <v>0.1549296603511057</v>
+        <v>0.1549296603511058</v>
       </c>
       <c r="C346" t="n">
         <v>0.1433223737400924</v>
@@ -6806,7 +6806,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="n">
-        <v>0.1428209419160845</v>
+        <v>0.1428209419160846</v>
       </c>
       <c r="C376" t="n">
         <v>0.1311687870524857</v>
@@ -6843,7 +6843,7 @@
         <v>0.1420888234665599</v>
       </c>
       <c r="C378" t="n">
-        <v>0.1304375745621028</v>
+        <v>0.1304375745621029</v>
       </c>
       <c r="D378" t="n">
         <v>0.963914373088685</v>
@@ -6976,7 +6976,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="n">
-        <v>0.1392440515649093</v>
+        <v>0.1392440515649094</v>
       </c>
       <c r="C386" t="n">
         <v>0.1276006932242196</v>
@@ -7234,7 +7234,7 @@
         <v>0.1342470290501603</v>
       </c>
       <c r="C401" t="n">
-        <v>0.1226354280147656</v>
+        <v>0.1226354280147655</v>
       </c>
       <c r="D401" t="n">
         <v>0.9655453618756371</v>
@@ -7299,7 +7299,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="n">
-        <v>0.1329833796330288</v>
+        <v>0.1329833796330289</v>
       </c>
       <c r="C405" t="n">
         <v>0.1213836646440986</v>
@@ -7316,7 +7316,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="n">
-        <v>0.1326717568894076</v>
+        <v>0.1326717568894075</v>
       </c>
       <c r="C406" t="n">
         <v>0.1210752237154526</v>
@@ -7588,7 +7588,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="n">
-        <v>0.1279064421883878</v>
+        <v>0.1279064421883879</v>
       </c>
       <c r="C422" t="n">
         <v>0.1163714990657313</v>
@@ -7676,7 +7676,7 @@
         <v>0.1264976292732219</v>
       </c>
       <c r="C427" t="n">
-        <v>0.1149857681263654</v>
+        <v>0.1149857681263655</v>
       </c>
       <c r="D427" t="n">
         <v>0.9663608562691132</v>
@@ -7877,7 +7877,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>0.1232595980923059</v>
+        <v>0.123259598092306</v>
       </c>
       <c r="C439" t="n">
         <v>0.1118098124626888</v>
@@ -8016,7 +8016,7 @@
         <v>0.1212061609056167</v>
       </c>
       <c r="C447" t="n">
-        <v>0.1098025826300613</v>
+        <v>0.1098025826300614</v>
       </c>
       <c r="D447" t="n">
         <v>0.9677879714576962</v>
@@ -8101,7 +8101,7 @@
         <v>0.1199628694188208</v>
       </c>
       <c r="C452" t="n">
-        <v>0.1085899738655364</v>
+        <v>0.1085899738655365</v>
       </c>
       <c r="D452" t="n">
         <v>0.9677879714576962</v>
@@ -8251,7 +8251,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="n">
-        <v>0.1177985113170484</v>
+        <v>0.1177985113170485</v>
       </c>
       <c r="C461" t="n">
         <v>0.1064840942094995</v>
@@ -8543,7 +8543,7 @@
         <v>0.113949443900799</v>
       </c>
       <c r="C478" t="n">
-        <v>0.1027557783014373</v>
+        <v>0.1027557783014374</v>
       </c>
       <c r="D478" t="n">
         <v>0.9686034658511723</v>
@@ -8781,7 +8781,7 @@
         <v>0.1109928118841997</v>
       </c>
       <c r="C492" t="n">
-        <v>0.09990743282749243</v>
+        <v>0.09990743282749244</v>
       </c>
       <c r="D492" t="n">
         <v>0.9690112130479103</v>
@@ -8849,7 +8849,7 @@
         <v>0.1101805807334581</v>
       </c>
       <c r="C496" t="n">
-        <v>0.09912744274890334</v>
+        <v>0.09912744274890337</v>
       </c>
       <c r="D496" t="n">
         <v>0.9690112130479103</v>
@@ -8934,7 +8934,7 @@
         <v>0.1091845480318014</v>
       </c>
       <c r="C501" t="n">
-        <v>0.09817246339804683</v>
+        <v>0.09817246339804682</v>
       </c>
       <c r="D501" t="n">
         <v>0.9688073394495413</v>
@@ -8968,7 +8968,7 @@
         <v>0.1087919752109073</v>
       </c>
       <c r="C503" t="n">
-        <v>0.09779653720048652</v>
+        <v>0.09779653720048651</v>
       </c>
       <c r="D503" t="n">
         <v>0.9688073394495413</v>
@@ -9050,10 +9050,10 @@
         <v>507</v>
       </c>
       <c r="B508" t="n">
-        <v>0.1078247471938257</v>
+        <v>0.1078247471938258</v>
       </c>
       <c r="C508" t="n">
-        <v>0.09687146613477685</v>
+        <v>0.09687146613477686</v>
       </c>
       <c r="D508" t="n">
         <v>0.9688073394495413</v>
@@ -9070,7 +9070,7 @@
         <v>0.1076336925002724</v>
       </c>
       <c r="C509" t="n">
-        <v>0.09668893293890275</v>
+        <v>0.09668893293890274</v>
       </c>
       <c r="D509" t="n">
         <v>0.9688073394495413</v>
@@ -9155,7 +9155,7 @@
         <v>0.1066900789772063</v>
       </c>
       <c r="C514" t="n">
-        <v>0.09578836054150958</v>
+        <v>0.09578836054150959</v>
       </c>
       <c r="D514" t="n">
         <v>0.9690112130479103</v>
@@ -9240,7 +9240,7 @@
         <v>0.1057654242448498</v>
       </c>
       <c r="C519" t="n">
-        <v>0.09490744249381425</v>
+        <v>0.09490744249381428</v>
       </c>
       <c r="D519" t="n">
         <v>0.9696228338430173</v>
@@ -9257,7 +9257,7 @@
         <v>0.1055827128607687</v>
       </c>
       <c r="C520" t="n">
-        <v>0.0947335587400365</v>
+        <v>0.09473355874003649</v>
       </c>
       <c r="D520" t="n">
         <v>0.9696228338430173</v>
@@ -9274,7 +9274,7 @@
         <v>0.1054007298578381</v>
       </c>
       <c r="C521" t="n">
-        <v>0.09456042947656738</v>
+        <v>0.09456042947656737</v>
       </c>
       <c r="D521" t="n">
         <v>0.9696228338430173</v>
@@ -9376,7 +9376,7 @@
         <v>0.1043238599794935</v>
       </c>
       <c r="C527" t="n">
-        <v>0.0935372150493884</v>
+        <v>0.09353721504938842</v>
       </c>
       <c r="D527" t="n">
         <v>0.9696228338430173</v>
@@ -9393,7 +9393,7 @@
         <v>0.1041468425529663</v>
       </c>
       <c r="C528" t="n">
-        <v>0.09336922653787652</v>
+        <v>0.09336922653787651</v>
       </c>
       <c r="D528" t="n">
         <v>0.9696228338430173</v>
@@ -9427,7 +9427,7 @@
         <v>0.1037948756743166</v>
       </c>
       <c r="C530" t="n">
-        <v>0.09303538914088613</v>
+        <v>0.09303538914088612</v>
       </c>
       <c r="D530" t="n">
         <v>0.9696228338430173</v>
@@ -9458,10 +9458,10 @@
         <v>531</v>
       </c>
       <c r="B532" t="n">
-        <v>0.1034456361624555</v>
+        <v>0.1034456361624554</v>
       </c>
       <c r="C532" t="n">
-        <v>0.09270437294457456</v>
+        <v>0.09270437294457459</v>
       </c>
       <c r="D532" t="n">
         <v>0.9696228338430173</v>
@@ -9495,7 +9495,7 @@
         <v>0.1030990886216013</v>
       </c>
       <c r="C534" t="n">
-        <v>0.09237614054250329</v>
+        <v>0.0923761405425033</v>
       </c>
       <c r="D534" t="n">
         <v>0.9696228338430173</v>
@@ -9512,7 +9512,7 @@
         <v>0.1029268134401175</v>
       </c>
       <c r="C535" t="n">
-        <v>0.09221305674541436</v>
+        <v>0.09221305674541437</v>
       </c>
       <c r="D535" t="n">
         <v>0.9696228338430173</v>
@@ -9529,7 +9529,7 @@
         <v>0.1027551982436487</v>
       </c>
       <c r="C536" t="n">
-        <v>0.09205065515102659</v>
+        <v>0.0920506551510266</v>
       </c>
       <c r="D536" t="n">
         <v>0.9696228338430173</v>
@@ -9597,7 +9597,7 @@
         <v>0.1020752526161168</v>
       </c>
       <c r="C540" t="n">
-        <v>0.0914077813088147</v>
+        <v>0.09140778130881468</v>
       </c>
       <c r="D540" t="n">
         <v>0.9698267074413863</v>
@@ -9648,7 +9648,7 @@
         <v>0.10157201793728</v>
       </c>
       <c r="C543" t="n">
-        <v>0.09093257212579413</v>
+        <v>0.09093257212579414</v>
       </c>
       <c r="D543" t="n">
         <v>0.9698267074413863</v>
@@ -9682,7 +9682,7 @@
         <v>0.1012396692498169</v>
       </c>
       <c r="C545" t="n">
-        <v>0.09061900919941886</v>
+        <v>0.09061900919941883</v>
       </c>
       <c r="D545" t="n">
         <v>0.9700305810397554</v>
@@ -9767,7 +9767,7 @@
         <v>0.1004195606731646</v>
       </c>
       <c r="C550" t="n">
-        <v>0.0898462093373897</v>
+        <v>0.08984620933738971</v>
       </c>
       <c r="D550" t="n">
         <v>0.9700305810397554</v>
@@ -9784,7 +9784,7 @@
         <v>0.1002573531378435</v>
       </c>
       <c r="C551" t="n">
-        <v>0.08969352082525092</v>
+        <v>0.08969352082525094</v>
       </c>
       <c r="D551" t="n">
         <v>0.9700305810397554</v>
@@ -9815,7 +9815,7 @@
         <v>552</v>
       </c>
       <c r="B553" t="n">
-        <v>0.09993472194627993</v>
+        <v>0.09993472194627992</v>
       </c>
       <c r="C553" t="n">
         <v>0.08938998325296743</v>
@@ -9835,7 +9835,7 @@
         <v>0.09977429085346401</v>
       </c>
       <c r="C554" t="n">
-        <v>0.08923912633762389</v>
+        <v>0.0892391263376239</v>
       </c>
       <c r="D554" t="n">
         <v>0.9700305810397554</v>
@@ -9869,7 +9869,7 @@
         <v>0.09945517930871534</v>
       </c>
       <c r="C556" t="n">
-        <v>0.08893921685030784</v>
+        <v>0.08893921685030785</v>
       </c>
       <c r="D556" t="n">
         <v>0.9700305810397554</v>
@@ -9886,7 +9886,7 @@
         <v>0.09929649160014174</v>
       </c>
       <c r="C557" t="n">
-        <v>0.08879015661370454</v>
+        <v>0.08879015661370453</v>
       </c>
       <c r="D557" t="n">
         <v>0.9702344546381244</v>
@@ -9900,7 +9900,7 @@
         <v>557</v>
       </c>
       <c r="B558" t="n">
-        <v>0.09913837781201877</v>
+        <v>0.09913837781201876</v>
       </c>
       <c r="C558" t="n">
         <v>0.0886416876572876</v>
@@ -9920,7 +9920,7 @@
         <v>0.09898083438913362</v>
       </c>
       <c r="C559" t="n">
-        <v>0.08849380622616312</v>
+        <v>0.08849380622616311</v>
       </c>
       <c r="D559" t="n">
         <v>0.9702344546381244</v>
@@ -9934,7 +9934,7 @@
         <v>559</v>
       </c>
       <c r="B560" t="n">
-        <v>0.09882385780503028</v>
+        <v>0.09882385780503025</v>
       </c>
       <c r="C560" t="n">
         <v>0.08834650859588888</v>
@@ -9968,10 +9968,10 @@
         <v>561</v>
       </c>
       <c r="B562" t="n">
-        <v>0.09851159118953645</v>
+        <v>0.09851159118953647</v>
       </c>
       <c r="C562" t="n">
-        <v>0.08805364999068746</v>
+        <v>0.08805364999068747</v>
       </c>
       <c r="D562" t="n">
         <v>0.9702344546381244</v>
@@ -9985,10 +9985,10 @@
         <v>562</v>
       </c>
       <c r="B563" t="n">
-        <v>0.09835629424663865</v>
+        <v>0.09835629424663866</v>
       </c>
       <c r="C563" t="n">
-        <v>0.08790808171660459</v>
+        <v>0.08790808171660461</v>
       </c>
       <c r="D563" t="n">
         <v>0.9702344546381244</v>
@@ -10002,7 +10002,7 @@
         <v>563</v>
       </c>
       <c r="B564" t="n">
-        <v>0.09820155031898958</v>
+        <v>0.0982015503189896</v>
       </c>
       <c r="C564" t="n">
         <v>0.08776308264450951</v>
@@ -10053,10 +10053,10 @@
         <v>566</v>
       </c>
       <c r="B567" t="n">
-        <v>0.0977406028972275</v>
+        <v>0.09774060289722748</v>
       </c>
       <c r="C567" t="n">
-        <v>0.08733146502020726</v>
+        <v>0.08733146502020725</v>
       </c>
       <c r="D567" t="n">
         <v>0.9702344546381244</v>
@@ -10070,7 +10070,7 @@
         <v>567</v>
       </c>
       <c r="B568" t="n">
-        <v>0.09758803743527555</v>
+        <v>0.09758803743527557</v>
       </c>
       <c r="C568" t="n">
         <v>0.08718870727904911</v>
@@ -10138,7 +10138,7 @@
         <v>571</v>
       </c>
       <c r="B572" t="n">
-        <v>0.09698310670378417</v>
+        <v>0.0969831067037842</v>
       </c>
       <c r="C572" t="n">
         <v>0.08662315815643566</v>
@@ -10158,7 +10158,7 @@
         <v>0.09683319072836558</v>
       </c>
       <c r="C573" t="n">
-        <v>0.08648312436631873</v>
+        <v>0.08648312436631875</v>
       </c>
       <c r="D573" t="n">
         <v>0.9702344546381244</v>
@@ -10175,7 +10175,7 @@
         <v>0.09668379509670588</v>
       </c>
       <c r="C574" t="n">
-        <v>0.08634362527907903</v>
+        <v>0.08634362527907904</v>
       </c>
       <c r="D574" t="n">
         <v>0.9702344546381244</v>
@@ -10192,7 +10192,7 @@
         <v>0.09653491668325476</v>
       </c>
       <c r="C575" t="n">
-        <v>0.08620465759467906</v>
+        <v>0.08620465759467905</v>
       </c>
       <c r="D575" t="n">
         <v>0.9702344546381244</v>
@@ -10223,7 +10223,7 @@
         <v>576</v>
       </c>
       <c r="B577" t="n">
-        <v>0.09623869913260245</v>
+        <v>0.09623869913260247</v>
       </c>
       <c r="C577" t="n">
         <v>0.08592830336528667</v>
@@ -10294,7 +10294,7 @@
         <v>0.09565233585190915</v>
       </c>
       <c r="C581" t="n">
-        <v>0.08538182942394944</v>
+        <v>0.08538182942394945</v>
       </c>
       <c r="D581" t="n">
         <v>0.9700305810397554</v>
@@ -10311,7 +10311,7 @@
         <v>0.09550699250636693</v>
       </c>
       <c r="C582" t="n">
-        <v>0.0852464913338702</v>
+        <v>0.08524649133387023</v>
       </c>
       <c r="D582" t="n">
         <v>0.9700305810397554</v>
@@ -10328,7 +10328,7 @@
         <v>0.09536214224908837</v>
       </c>
       <c r="C583" t="n">
-        <v>0.08511165917164225</v>
+        <v>0.08511165917164226</v>
       </c>
       <c r="D583" t="n">
         <v>0.9700305810397554</v>
@@ -10379,7 +10379,7 @@
         <v>0.09493052101877657</v>
       </c>
       <c r="C586" t="n">
-        <v>0.0847101676508013</v>
+        <v>0.08471016765080128</v>
       </c>
       <c r="D586" t="n">
         <v>0.9700305810397554</v>
@@ -10393,10 +10393,10 @@
         <v>586</v>
       </c>
       <c r="B587" t="n">
-        <v>0.09478761423993998</v>
+        <v>0.09478761423993996</v>
       </c>
       <c r="C587" t="n">
-        <v>0.08457732871871748</v>
+        <v>0.08457732871871751</v>
       </c>
       <c r="D587" t="n">
         <v>0.9700305810397554</v>
@@ -10410,7 +10410,7 @@
         <v>587</v>
       </c>
       <c r="B588" t="n">
-        <v>0.09464518622478957</v>
+        <v>0.09464518622478958</v>
       </c>
       <c r="C588" t="n">
         <v>0.08444498059309682</v>
@@ -10478,7 +10478,7 @@
         <v>591</v>
       </c>
       <c r="B592" t="n">
-        <v>0.09408020616769742</v>
+        <v>0.09408020616769745</v>
       </c>
       <c r="C592" t="n">
         <v>0.08392043743072147</v>
@@ -10495,10 +10495,10 @@
         <v>592</v>
       </c>
       <c r="B593" t="n">
-        <v>0.09394013043501179</v>
+        <v>0.0939401304350118</v>
       </c>
       <c r="C593" t="n">
-        <v>0.08379049949395458</v>
+        <v>0.08379049949395459</v>
       </c>
       <c r="D593" t="n">
         <v>0.9700305810397554</v>
@@ -10532,7 +10532,7 @@
         <v>0.09366136319813816</v>
       </c>
       <c r="C595" t="n">
-        <v>0.08353204108603975</v>
+        <v>0.08353204108603976</v>
       </c>
       <c r="D595" t="n">
         <v>0.9700305810397554</v>
@@ -10580,7 +10580,7 @@
         <v>597</v>
       </c>
       <c r="B598" t="n">
-        <v>0.09324663317539268</v>
+        <v>0.09324663317539271</v>
       </c>
       <c r="C598" t="n">
         <v>0.08314785519531522</v>
@@ -10600,7 +10600,7 @@
         <v>0.09310929160252364</v>
       </c>
       <c r="C599" t="n">
-        <v>0.08302071599047672</v>
+        <v>0.08302071599047671</v>
       </c>
       <c r="D599" t="n">
         <v>0.9700305810397554</v>
@@ -10648,7 +10648,7 @@
         <v>601</v>
       </c>
       <c r="B602" t="n">
-        <v>0.09269993623123841</v>
+        <v>0.0926999362312384</v>
       </c>
       <c r="C602" t="n">
         <v>0.08264202870292246</v>
@@ -10682,7 +10682,7 @@
         <v>603</v>
       </c>
       <c r="B604" t="n">
-        <v>0.09242923186570041</v>
+        <v>0.09242923186570043</v>
       </c>
       <c r="C604" t="n">
         <v>0.08239181914502466</v>
@@ -10699,10 +10699,10 @@
         <v>604</v>
       </c>
       <c r="B605" t="n">
-        <v>0.09229453197674199</v>
+        <v>0.09229453197674201</v>
       </c>
       <c r="C605" t="n">
-        <v>0.08226738107185536</v>
+        <v>0.08226738107185537</v>
       </c>
       <c r="D605" t="n">
         <v>0.9700305810397554</v>
@@ -10767,7 +10767,7 @@
         <v>608</v>
       </c>
       <c r="B609" t="n">
-        <v>0.09176002404547817</v>
+        <v>0.09176002404547819</v>
       </c>
       <c r="C609" t="n">
         <v>0.08177401332979077</v>
@@ -10787,7 +10787,7 @@
         <v>0.09162745794012563</v>
       </c>
       <c r="C610" t="n">
-        <v>0.08165175483801289</v>
+        <v>0.08165175483801286</v>
       </c>
       <c r="D610" t="n">
         <v>0.9706422018348624</v>
@@ -10804,7 +10804,7 @@
         <v>0.09149531143827531</v>
       </c>
       <c r="C611" t="n">
-        <v>0.08152992471378873</v>
+        <v>0.08152992471378874</v>
       </c>
       <c r="D611" t="n">
         <v>0.9706422018348624</v>
@@ -10835,7 +10835,7 @@
         <v>612</v>
       </c>
       <c r="B613" t="n">
-        <v>0.0912322678940479</v>
+        <v>0.09123226789404788</v>
       </c>
       <c r="C613" t="n">
         <v>0.08128753970022125</v>
@@ -10872,7 +10872,7 @@
         <v>0.09097087488746917</v>
       </c>
       <c r="C615" t="n">
-        <v>0.08104683874028931</v>
+        <v>0.08104683874028933</v>
       </c>
       <c r="D615" t="n">
         <v>0.9706422018348624</v>
@@ -10940,7 +10940,7 @@
         <v>0.09045296777752491</v>
       </c>
       <c r="C619" t="n">
-        <v>0.08057041225654615</v>
+        <v>0.08057041225654614</v>
       </c>
       <c r="D619" t="n">
         <v>0.9706422018348624</v>
@@ -10954,7 +10954,7 @@
         <v>619</v>
       </c>
       <c r="B620" t="n">
-        <v>0.09032449440772447</v>
+        <v>0.09032449440772448</v>
       </c>
       <c r="C620" t="n">
         <v>0.08045232843507906</v>
@@ -10971,10 +10971,10 @@
         <v>620</v>
       </c>
       <c r="B621" t="n">
-        <v>0.09019641800043982</v>
+        <v>0.0901964180004398</v>
       </c>
       <c r="C621" t="n">
-        <v>0.08033464909003542</v>
+        <v>0.08033464909003543</v>
       </c>
       <c r="D621" t="n">
         <v>0.9706422018348624</v>
@@ -10988,10 +10988,10 @@
         <v>621</v>
       </c>
       <c r="B622" t="n">
-        <v>0.09006873638425625</v>
+        <v>0.09006873638425628</v>
       </c>
       <c r="C622" t="n">
-        <v>0.08021737193022897</v>
+        <v>0.080217371930229</v>
       </c>
       <c r="D622" t="n">
         <v>0.9706422018348624</v>
@@ -11008,7 +11008,7 @@
         <v>0.08994144740402141</v>
       </c>
       <c r="C623" t="n">
-        <v>0.08010049468165427</v>
+        <v>0.08010049468165428</v>
       </c>
       <c r="D623" t="n">
         <v>0.9706422018348624</v>
@@ -11022,10 +11022,10 @@
         <v>623</v>
       </c>
       <c r="B624" t="n">
-        <v>0.08981454892070237</v>
+        <v>0.08981454892070238</v>
       </c>
       <c r="C624" t="n">
-        <v>0.07998401508733546</v>
+        <v>0.07998401508733549</v>
       </c>
       <c r="D624" t="n">
         <v>0.9706422018348624</v>
@@ -11073,7 +11073,7 @@
         <v>626</v>
       </c>
       <c r="B627" t="n">
-        <v>0.08943617530074328</v>
+        <v>0.0894361753007433</v>
       </c>
       <c r="C627" t="n">
         <v>0.07963693991246962</v>
@@ -11212,7 +11212,7 @@
         <v>0.08844384235485947</v>
       </c>
       <c r="C635" t="n">
-        <v>0.07872835584018853</v>
+        <v>0.07872835584018852</v>
       </c>
       <c r="D635" t="n">
         <v>0.9706422018348624</v>
@@ -11229,7 +11229,7 @@
         <v>0.0883214686684245</v>
       </c>
       <c r="C636" t="n">
-        <v>0.07861647805167893</v>
+        <v>0.0786164780516789</v>
       </c>
       <c r="D636" t="n">
         <v>0.9706422018348624</v>
@@ -11246,7 +11246,7 @@
         <v>0.08819945907581399</v>
       </c>
       <c r="C637" t="n">
-        <v>0.07850497006030038</v>
+        <v>0.0785049700603004</v>
       </c>
       <c r="D637" t="n">
         <v>0.9706422018348624</v>
@@ -11277,7 +11277,7 @@
         <v>638</v>
       </c>
       <c r="B639" t="n">
-        <v>0.08795652447575487</v>
+        <v>0.08795652447575489</v>
       </c>
       <c r="C639" t="n">
         <v>0.07828305534935122</v>
@@ -11297,7 +11297,7 @@
         <v>0.08783559565536367</v>
       </c>
       <c r="C640" t="n">
-        <v>0.07817264460718745</v>
+        <v>0.07817264460718747</v>
       </c>
       <c r="D640" t="n">
         <v>0.9706422018348624</v>
@@ -11328,10 +11328,10 @@
         <v>641</v>
       </c>
       <c r="B642" t="n">
-        <v>0.08759480554586248</v>
+        <v>0.08759480554586249</v>
       </c>
       <c r="C642" t="n">
-        <v>0.07795290640324905</v>
+        <v>0.07795290640324903</v>
       </c>
       <c r="D642" t="n">
         <v>0.9706422018348624</v>
@@ -11379,7 +11379,7 @@
         <v>644</v>
       </c>
       <c r="B645" t="n">
-        <v>0.08723626133680266</v>
+        <v>0.08723626133680269</v>
       </c>
       <c r="C645" t="n">
         <v>0.07762597789379268</v>
@@ -11396,7 +11396,7 @@
         <v>645</v>
       </c>
       <c r="B646" t="n">
-        <v>0.08711744351677275</v>
+        <v>0.08711744351677278</v>
       </c>
       <c r="C646" t="n">
         <v>0.07751770832822971</v>
@@ -11413,10 +11413,10 @@
         <v>646</v>
       </c>
       <c r="B647" t="n">
-        <v>0.08699897113603537</v>
+        <v>0.08699897113603539</v>
       </c>
       <c r="C647" t="n">
-        <v>0.07740978888017237</v>
+        <v>0.07740978888017239</v>
       </c>
       <c r="D647" t="n">
         <v>0.9710499490316004</v>
@@ -11447,7 +11447,7 @@
         <v>648</v>
       </c>
       <c r="B649" t="n">
-        <v>0.08676305553882166</v>
+        <v>0.08676305553882167</v>
       </c>
       <c r="C649" t="n">
         <v>0.0771949927903352</v>
@@ -11464,7 +11464,7 @@
         <v>649</v>
       </c>
       <c r="B650" t="n">
-        <v>0.08664560877782639</v>
+        <v>0.0866456087778264</v>
       </c>
       <c r="C650" t="n">
         <v>0.07708811240955281</v>
@@ -11532,10 +11532,10 @@
         <v>653</v>
       </c>
       <c r="B654" t="n">
-        <v>0.08617918789200399</v>
+        <v>0.08617918789200402</v>
       </c>
       <c r="C654" t="n">
-        <v>0.07666399898606167</v>
+        <v>0.07666399898606169</v>
       </c>
       <c r="D654" t="n">
         <v>0.9712538226299694</v>
@@ -11552,7 +11552,7 @@
         <v>0.08606341560118035</v>
       </c>
       <c r="C655" t="n">
-        <v>0.07655881357428929</v>
+        <v>0.07655881357428931</v>
       </c>
       <c r="D655" t="n">
         <v>0.9712538226299694</v>
@@ -11566,10 +11566,10 @@
         <v>655</v>
       </c>
       <c r="B656" t="n">
-        <v>0.08594797308219934</v>
+        <v>0.08594797308219936</v>
       </c>
       <c r="C656" t="n">
-        <v>0.07645396175343683</v>
+        <v>0.07645396175343684</v>
       </c>
       <c r="D656" t="n">
         <v>0.9712538226299694</v>
@@ -11583,7 +11583,7 @@
         <v>656</v>
       </c>
       <c r="B657" t="n">
-        <v>0.08583285865613798</v>
+        <v>0.08583285865613799</v>
       </c>
       <c r="C657" t="n">
         <v>0.07634944175263603</v>
@@ -11600,7 +11600,7 @@
         <v>657</v>
       </c>
       <c r="B658" t="n">
-        <v>0.08571807065606844</v>
+        <v>0.08571807065606846</v>
       </c>
       <c r="C658" t="n">
         <v>0.07624525181369665</v>
@@ -11654,7 +11654,7 @@
         <v>0.08537564872032234</v>
       </c>
       <c r="C661" t="n">
-        <v>0.07593464497406473</v>
+        <v>0.07593464497406474</v>
       </c>
       <c r="D661" t="n">
         <v>0.9712538226299694</v>
@@ -11702,10 +11702,10 @@
         <v>663</v>
       </c>
       <c r="B664" t="n">
-        <v>0.08503610573937297</v>
+        <v>0.08503610573937298</v>
       </c>
       <c r="C664" t="n">
-        <v>0.07562694659105533</v>
+        <v>0.07562694659105536</v>
       </c>
       <c r="D664" t="n">
         <v>0.9712538226299694</v>
@@ -11719,10 +11719,10 @@
         <v>664</v>
       </c>
       <c r="B665" t="n">
-        <v>0.08492355703364911</v>
+        <v>0.08492355703364912</v>
       </c>
       <c r="C665" t="n">
-        <v>0.07552501889845868</v>
+        <v>0.0755250188984587</v>
       </c>
       <c r="D665" t="n">
         <v>0.9712538226299694</v>
@@ -11753,10 +11753,10 @@
         <v>666</v>
       </c>
       <c r="B667" t="n">
-        <v>0.0846993985897522</v>
+        <v>0.08469939858975221</v>
       </c>
       <c r="C667" t="n">
-        <v>0.07532211118465629</v>
+        <v>0.0753221111846563</v>
       </c>
       <c r="D667" t="n">
         <v>0.9712538226299694</v>
@@ -11770,10 +11770,10 @@
         <v>667</v>
       </c>
       <c r="B668" t="n">
-        <v>0.08458778573568423</v>
+        <v>0.08458778573568422</v>
       </c>
       <c r="C668" t="n">
-        <v>0.07522112787749365</v>
+        <v>0.07522112787749363</v>
       </c>
       <c r="D668" t="n">
         <v>0.9712538226299694</v>
@@ -11838,10 +11838,10 @@
         <v>671</v>
       </c>
       <c r="B672" t="n">
-        <v>0.08414440759539675</v>
+        <v>0.08414440759539676</v>
       </c>
       <c r="C672" t="n">
-        <v>0.07482029384909851</v>
+        <v>0.07482029384909852</v>
       </c>
       <c r="D672" t="n">
         <v>0.9712538226299694</v>
@@ -11855,10 +11855,10 @@
         <v>672</v>
       </c>
       <c r="B673" t="n">
-        <v>0.08403432380603268</v>
+        <v>0.08403432380603269</v>
       </c>
       <c r="C673" t="n">
-        <v>0.07472085215608423</v>
+        <v>0.07472085215608425</v>
       </c>
       <c r="D673" t="n">
         <v>0.9712538226299694</v>
@@ -11892,7 +11892,7 @@
         <v>0.08381505866739578</v>
       </c>
       <c r="C675" t="n">
-        <v>0.0745228779229738</v>
+        <v>0.07452287792297378</v>
       </c>
       <c r="D675" t="n">
         <v>0.9712538226299694</v>
@@ -11906,7 +11906,7 @@
         <v>675</v>
       </c>
       <c r="B676" t="n">
-        <v>0.083705874372655</v>
+        <v>0.08370587437265502</v>
       </c>
       <c r="C676" t="n">
         <v>0.07442434227718303</v>
@@ -11940,10 +11940,10 @@
         <v>677</v>
       </c>
       <c r="B678" t="n">
-        <v>0.08348839504536808</v>
+        <v>0.08348839504536809</v>
       </c>
       <c r="C678" t="n">
-        <v>0.07422816624405616</v>
+        <v>0.07422816624405618</v>
       </c>
       <c r="D678" t="n">
         <v>0.9714576962283384</v>
@@ -11957,10 +11957,10 @@
         <v>678</v>
       </c>
       <c r="B679" t="n">
-        <v>0.08338009712836315</v>
+        <v>0.08338009712836318</v>
       </c>
       <c r="C679" t="n">
-        <v>0.07413052281557948</v>
+        <v>0.0741305228155795</v>
       </c>
       <c r="D679" t="n">
         <v>0.9714576962283384</v>
@@ -11974,7 +11974,7 @@
         <v>679</v>
       </c>
       <c r="B680" t="n">
-        <v>0.08327209180279584</v>
+        <v>0.08327209180279585</v>
       </c>
       <c r="C680" t="n">
         <v>0.07403317376935481</v>
@@ -11994,7 +11994,7 @@
         <v>0.08316437765128863</v>
       </c>
       <c r="C681" t="n">
-        <v>0.07393611761111286</v>
+        <v>0.07393611761111288</v>
       </c>
       <c r="D681" t="n">
         <v>0.9714576962283384</v>
@@ -12008,7 +12008,7 @@
         <v>681</v>
       </c>
       <c r="B682" t="n">
-        <v>0.08305695326625639</v>
+        <v>0.08305695326625638</v>
       </c>
       <c r="C682" t="n">
         <v>0.07383935285694902</v>
@@ -12042,10 +12042,10 @@
         <v>683</v>
       </c>
       <c r="B684" t="n">
-        <v>0.08284296821375019</v>
+        <v>0.0828429682137502</v>
       </c>
       <c r="C684" t="n">
-        <v>0.07364669167654955</v>
+        <v>0.07364669167654957</v>
       </c>
       <c r="D684" t="n">
         <v>0.9714576962283384</v>
@@ -12096,7 +12096,7 @@
         <v>0.08252412924801771</v>
       </c>
       <c r="C687" t="n">
-        <v>0.07335984892548915</v>
+        <v>0.07335984892548916</v>
       </c>
       <c r="D687" t="n">
         <v>0.9714576962283384</v>
@@ -12110,7 +12110,7 @@
         <v>687</v>
       </c>
       <c r="B688" t="n">
-        <v>0.08241841444076703</v>
+        <v>0.08241841444076704</v>
       </c>
       <c r="C688" t="n">
         <v>0.07326480200357549</v>
@@ -12127,10 +12127,10 @@
         <v>688</v>
       </c>
       <c r="B689" t="n">
-        <v>0.0823129798143466</v>
+        <v>0.08231297981434661</v>
       </c>
       <c r="C689" t="n">
-        <v>0.07317003638155715</v>
+        <v>0.07317003638155713</v>
       </c>
       <c r="D689" t="n">
         <v>0.9714576962283384</v>
@@ -12144,7 +12144,7 @@
         <v>689</v>
       </c>
       <c r="B690" t="n">
-        <v>0.08220782403664703</v>
+        <v>0.08220782403664705</v>
       </c>
       <c r="C690" t="n">
         <v>0.07307555065544462</v>
@@ -12161,7 +12161,7 @@
         <v>690</v>
       </c>
       <c r="B691" t="n">
-        <v>0.08210294578464691</v>
+        <v>0.08210294578464693</v>
       </c>
       <c r="C691" t="n">
         <v>0.07298134343087442</v>
@@ -12215,7 +12215,7 @@
         <v>0.08178996308738702</v>
       </c>
       <c r="C694" t="n">
-        <v>0.07270037896553457</v>
+        <v>0.07270037896553458</v>
       </c>
       <c r="D694" t="n">
         <v>0.9714576962283384</v>
@@ -12229,7 +12229,7 @@
         <v>694</v>
       </c>
       <c r="B695" t="n">
-        <v>0.08168618188713409</v>
+        <v>0.0816861818871341</v>
       </c>
       <c r="C695" t="n">
         <v>0.07260727199329567</v>
@@ -12263,7 +12263,7 @@
         <v>696</v>
       </c>
       <c r="B697" t="n">
-        <v>0.08147943134957145</v>
+        <v>0.08147943134957147</v>
       </c>
       <c r="C697" t="n">
         <v>0.07242187172480069</v>
@@ -12283,7 +12283,7 @@
         <v>0.08137645948077213</v>
       </c>
       <c r="C698" t="n">
-        <v>0.07232957576118942</v>
+        <v>0.07232957576118945</v>
       </c>
       <c r="D698" t="n">
         <v>0.9714576962283384</v>
@@ -12317,7 +12317,7 @@
         <v>0.0811713162783505</v>
       </c>
       <c r="C700" t="n">
-        <v>0.07214578557461657</v>
+        <v>0.07214578557461655</v>
       </c>
       <c r="D700" t="n">
         <v>0.9714576962283384</v>
@@ -12382,7 +12382,7 @@
         <v>703</v>
       </c>
       <c r="B704" t="n">
-        <v>0.08076419745982048</v>
+        <v>0.08076419745982047</v>
       </c>
       <c r="C704" t="n">
         <v>0.07178137576072148</v>
@@ -12402,7 +12402,7 @@
         <v>0.08066307056644927</v>
       </c>
       <c r="C705" t="n">
-        <v>0.07169092635846953</v>
+        <v>0.07169092635846955</v>
       </c>
       <c r="D705" t="n">
         <v>0.9714576962283384</v>
@@ -12419,7 +12419,7 @@
         <v>0.08056220239495319</v>
       </c>
       <c r="C706" t="n">
-        <v>0.07160073564596016</v>
+        <v>0.07160073564596017</v>
       </c>
       <c r="D706" t="n">
         <v>0.9714576962283384</v>
@@ -12433,10 +12433,10 @@
         <v>706</v>
       </c>
       <c r="B707" t="n">
-        <v>0.08046159175804465</v>
+        <v>0.08046159175804467</v>
       </c>
       <c r="C707" t="n">
-        <v>0.07151080237269612</v>
+        <v>0.07151080237269614</v>
       </c>
       <c r="D707" t="n">
         <v>0.9714576962283384</v>
@@ -12450,7 +12450,7 @@
         <v>707</v>
       </c>
       <c r="B708" t="n">
-        <v>0.08036123747634873</v>
+        <v>0.08036123747634874</v>
       </c>
       <c r="C708" t="n">
         <v>0.07142112529657262</v>
@@ -12467,7 +12467,7 @@
         <v>708</v>
       </c>
       <c r="B709" t="n">
-        <v>0.08026113837833979</v>
+        <v>0.0802611383783398</v>
       </c>
       <c r="C709" t="n">
         <v>0.07133170318381078</v>
@@ -12521,7 +12521,7 @@
         <v>0.07996236058760602</v>
       </c>
       <c r="C712" t="n">
-        <v>0.07106495441141528</v>
+        <v>0.07106495441141526</v>
       </c>
       <c r="D712" t="n">
         <v>0.9714576962283384</v>
@@ -12572,7 +12572,7 @@
         <v>0.07966583801561561</v>
       </c>
       <c r="C715" t="n">
-        <v>0.07080045667879861</v>
+        <v>0.07080045667879863</v>
       </c>
       <c r="D715" t="n">
         <v>0.9714576962283384</v>
@@ -12586,7 +12586,7 @@
         <v>715</v>
       </c>
       <c r="B716" t="n">
-        <v>0.07956749304702206</v>
+        <v>0.07956749304702207</v>
       </c>
       <c r="C716" t="n">
         <v>0.07071278544944617</v>
@@ -12654,10 +12654,10 @@
         <v>719</v>
       </c>
       <c r="B720" t="n">
-        <v>0.07917656303907124</v>
+        <v>0.07917656303907122</v>
       </c>
       <c r="C720" t="n">
-        <v>0.07036454280384853</v>
+        <v>0.07036454280384855</v>
       </c>
       <c r="D720" t="n">
         <v>0.9714576962283384</v>
@@ -12674,7 +12674,7 @@
         <v>0.07907943753963276</v>
       </c>
       <c r="C721" t="n">
-        <v>0.07027808695913616</v>
+        <v>0.07027808695913618</v>
       </c>
       <c r="D721" t="n">
         <v>0.9716615698267075</v>
@@ -12691,7 +12691,7 @@
         <v>0.07898255268060472</v>
       </c>
       <c r="C722" t="n">
-        <v>0.07019187076714402</v>
+        <v>0.070191870767144</v>
       </c>
       <c r="D722" t="n">
         <v>0.9718654434250764</v>
@@ -12708,7 +12708,7 @@
         <v>0.07888590739403274</v>
       </c>
       <c r="C723" t="n">
-        <v>0.07010589310400568</v>
+        <v>0.0701058931040057</v>
       </c>
       <c r="D723" t="n">
         <v>0.9718654434250764</v>
@@ -12722,10 +12722,10 @@
         <v>723</v>
       </c>
       <c r="B724" t="n">
-        <v>0.07878950061893165</v>
+        <v>0.07878950061893167</v>
       </c>
       <c r="C724" t="n">
-        <v>0.07002015285325375</v>
+        <v>0.07002015285325373</v>
       </c>
       <c r="D724" t="n">
         <v>0.9718654434250764</v>
@@ -12756,7 +12756,7 @@
         <v>725</v>
       </c>
       <c r="B726" t="n">
-        <v>0.07859739839372229</v>
+        <v>0.0785973983937223</v>
       </c>
       <c r="C726" t="n">
         <v>0.06984938015969049</v>
@@ -12773,7 +12773,7 @@
         <v>726</v>
       </c>
       <c r="B727" t="n">
-        <v>0.0785017008560038</v>
+        <v>0.07850170085600382</v>
       </c>
       <c r="C727" t="n">
         <v>0.06976434552042581</v>
@@ -12810,7 +12810,7 @@
         <v>0.07831100776205753</v>
       </c>
       <c r="C729" t="n">
-        <v>0.06959497421967703</v>
+        <v>0.06959497421967704</v>
       </c>
       <c r="D729" t="n">
         <v>0.9720693170234455</v>
@@ -12827,7 +12827,7 @@
         <v>0.07821601015859528</v>
       </c>
       <c r="C730" t="n">
-        <v>0.06951063540461173</v>
+        <v>0.06951063540461172</v>
       </c>
       <c r="D730" t="n">
         <v>0.9720693170234455</v>
@@ -12841,10 +12841,10 @@
         <v>730</v>
       </c>
       <c r="B731" t="n">
-        <v>0.07812124383035157</v>
+        <v>0.07812124383035156</v>
       </c>
       <c r="C731" t="n">
-        <v>0.06942652638908212</v>
+        <v>0.06942652638908213</v>
       </c>
       <c r="D731" t="n">
         <v>0.9720693170234455</v>
@@ -12858,10 +12858,10 @@
         <v>731</v>
       </c>
       <c r="B732" t="n">
-        <v>0.07802670777018428</v>
+        <v>0.07802670777018429</v>
       </c>
       <c r="C732" t="n">
-        <v>0.06934264611379246</v>
+        <v>0.06934264611379244</v>
       </c>
       <c r="D732" t="n">
         <v>0.9720693170234455</v>
@@ -12875,7 +12875,7 @@
         <v>732</v>
       </c>
       <c r="B733" t="n">
-        <v>0.07793240097745044</v>
+        <v>0.07793240097745045</v>
       </c>
       <c r="C733" t="n">
         <v>0.06925899352634857</v>
@@ -12892,7 +12892,7 @@
         <v>733</v>
       </c>
       <c r="B734" t="n">
-        <v>0.0778383224579564</v>
+        <v>0.07783832245795641</v>
       </c>
       <c r="C734" t="n">
         <v>0.06917556758120509</v>
@@ -12912,7 +12912,7 @@
         <v>0.07774447122390864</v>
       </c>
       <c r="C735" t="n">
-        <v>0.06909236723961318</v>
+        <v>0.06909236723961316</v>
       </c>
       <c r="D735" t="n">
         <v>0.9720693170234455</v>
@@ -12977,7 +12977,7 @@
         <v>738</v>
       </c>
       <c r="B739" t="n">
-        <v>0.07737131960759334</v>
+        <v>0.07737131960759336</v>
       </c>
       <c r="C739" t="n">
         <v>0.06876180136877331</v>
@@ -12997,7 +12997,7 @@
         <v>0.07727859020448734</v>
       </c>
       <c r="C740" t="n">
-        <v>0.06867971369798304</v>
+        <v>0.06867971369798305</v>
       </c>
       <c r="D740" t="n">
         <v>0.9722731906218145</v>
@@ -13045,7 +13045,7 @@
         <v>742</v>
       </c>
       <c r="B743" t="n">
-        <v>0.07700172716617798</v>
+        <v>0.07700172716617801</v>
       </c>
       <c r="C743" t="n">
         <v>0.06843476378710704</v>
@@ -13099,7 +13099,7 @@
         <v>0.07672683224214223</v>
       </c>
       <c r="C746" t="n">
-        <v>0.06819176288433007</v>
+        <v>0.06819176288433006</v>
       </c>
       <c r="D746" t="n">
         <v>0.9722731906218145</v>
@@ -13116,7 +13116,7 @@
         <v>0.0766356336499556</v>
       </c>
       <c r="C747" t="n">
-        <v>0.06811119116751854</v>
+        <v>0.06811119116751857</v>
       </c>
       <c r="D747" t="n">
         <v>0.9722731906218145</v>
@@ -13130,10 +13130,10 @@
         <v>747</v>
       </c>
       <c r="B748" t="n">
-        <v>0.07654465006272761</v>
+        <v>0.07654465006272762</v>
       </c>
       <c r="C748" t="n">
-        <v>0.06803083214604998</v>
+        <v>0.06803083214604996</v>
       </c>
       <c r="D748" t="n">
         <v>0.9722731906218145</v>
@@ -13147,7 +13147,7 @@
         <v>748</v>
       </c>
       <c r="B749" t="n">
-        <v>0.07645388057734837</v>
+        <v>0.07645388057734838</v>
       </c>
       <c r="C749" t="n">
         <v>0.06795068487109111</v>
@@ -13184,7 +13184,7 @@
         <v>0.07627298032822984</v>
       </c>
       <c r="C751" t="n">
-        <v>0.06779102179565445</v>
+        <v>0.06779102179565447</v>
       </c>
       <c r="D751" t="n">
         <v>0.9722731906218145</v>
@@ -13198,10 +13198,10 @@
         <v>751</v>
       </c>
       <c r="B752" t="n">
-        <v>0.07618284778667772</v>
+        <v>0.07618284778667769</v>
       </c>
       <c r="C752" t="n">
-        <v>0.06771150412765937</v>
+        <v>0.06771150412765939</v>
       </c>
       <c r="D752" t="n">
         <v>0.9722731906218145</v>
@@ -13269,7 +13269,7 @@
         <v>0.07582441435983511</v>
       </c>
       <c r="C756" t="n">
-        <v>0.06739550440918309</v>
+        <v>0.0673955044091831</v>
       </c>
       <c r="D756" t="n">
         <v>0.9724770642201835</v>
@@ -13337,7 +13337,7 @@
         <v>0.07546929430817659</v>
       </c>
       <c r="C760" t="n">
-        <v>0.06708277473238643</v>
+        <v>0.06708277473238641</v>
       </c>
       <c r="D760" t="n">
         <v>0.9728848114169215</v>
@@ -13371,7 +13371,7 @@
         <v>0.0752929598407287</v>
       </c>
       <c r="C762" t="n">
-        <v>0.06692761835515837</v>
+        <v>0.06692761835515838</v>
       </c>
       <c r="D762" t="n">
         <v>0.9728848114169215</v>
@@ -13439,7 +13439,7 @@
         <v>0.07494270884502086</v>
       </c>
       <c r="C766" t="n">
-        <v>0.06661968769543804</v>
+        <v>0.06661968769543807</v>
       </c>
       <c r="D766" t="n">
         <v>0.9730886850152906</v>
@@ -13453,7 +13453,7 @@
         <v>766</v>
       </c>
       <c r="B767" t="n">
-        <v>0.0748556450776668</v>
+        <v>0.07485564507766682</v>
       </c>
       <c r="C767" t="n">
         <v>0.06654319630877766</v>
@@ -13507,7 +13507,7 @@
         <v>0.07459563848896704</v>
       </c>
       <c r="C770" t="n">
-        <v>0.06631488773962872</v>
+        <v>0.06631488773962874</v>
       </c>
       <c r="D770" t="n">
         <v>0.9732925586136595</v>
@@ -13538,7 +13538,7 @@
         <v>771</v>
       </c>
       <c r="B772" t="n">
-        <v>0.07442328012186847</v>
+        <v>0.07442328012186848</v>
       </c>
       <c r="C772" t="n">
         <v>0.06616364506075036</v>
@@ -13555,7 +13555,7 @@
         <v>772</v>
       </c>
       <c r="B773" t="n">
-        <v>0.07433739240084994</v>
+        <v>0.07433739240084995</v>
       </c>
       <c r="C773" t="n">
         <v>0.0660883101710726</v>
@@ -13572,7 +13572,7 @@
         <v>773</v>
       </c>
       <c r="B774" t="n">
-        <v>0.07425169795719944</v>
+        <v>0.07425169795719942</v>
       </c>
       <c r="C774" t="n">
         <v>0.06601316516630959</v>
@@ -13589,7 +13589,7 @@
         <v>774</v>
       </c>
       <c r="B775" t="n">
-        <v>0.07416619602364817</v>
+        <v>0.07416619602364816</v>
       </c>
       <c r="C775" t="n">
         <v>0.06593820924157812</v>
@@ -13606,7 +13606,7 @@
         <v>775</v>
       </c>
       <c r="B776" t="n">
-        <v>0.07408088583766358</v>
+        <v>0.07408088583766356</v>
       </c>
       <c r="C776" t="n">
         <v>0.06586344159700029</v>
@@ -13626,7 +13626,7 @@
         <v>0.07399576664141636</v>
       </c>
       <c r="C777" t="n">
-        <v>0.06578886143766685</v>
+        <v>0.06578886143766687</v>
       </c>
       <c r="D777" t="n">
         <v>0.9739041794087666</v>
@@ -13660,7 +13660,7 @@
         <v>0.07382609821013589</v>
       </c>
       <c r="C779" t="n">
-        <v>0.06564026041972419</v>
+        <v>0.06564026041972416</v>
       </c>
       <c r="D779" t="n">
         <v>0.9739041794087666</v>
@@ -13694,7 +13694,7 @@
         <v>0.07365718475999548</v>
       </c>
       <c r="C781" t="n">
-        <v>0.06549239992648803</v>
+        <v>0.06549239992648802</v>
       </c>
       <c r="D781" t="n">
         <v>0.9739041794087666</v>
@@ -13711,7 +13711,7 @@
         <v>0.07357300930732484</v>
       </c>
       <c r="C782" t="n">
-        <v>0.06541874544113613</v>
+        <v>0.06541874544113614</v>
       </c>
       <c r="D782" t="n">
         <v>0.9739041794087666</v>
@@ -13745,7 +13745,7 @@
         <v>0.07340521729530501</v>
       </c>
       <c r="C784" t="n">
-        <v>0.06527198416370862</v>
+        <v>0.06527198416370861</v>
       </c>
       <c r="D784" t="n">
         <v>0.9739041794087666</v>
@@ -13762,7 +13762,7 @@
         <v>0.07332159928878496</v>
       </c>
       <c r="C785" t="n">
-        <v>0.06519887585407654</v>
+        <v>0.06519887585407655</v>
       </c>
       <c r="D785" t="n">
         <v>0.9739041794087666</v>
@@ -13776,10 +13776,10 @@
         <v>785</v>
       </c>
       <c r="B786" t="n">
-        <v>0.07323816565786152</v>
+        <v>0.07323816565786155</v>
       </c>
       <c r="C786" t="n">
-        <v>0.06512594809324072</v>
+        <v>0.06512594809324074</v>
       </c>
       <c r="D786" t="n">
         <v>0.9739041794087666</v>
@@ -13793,7 +13793,7 @@
         <v>786</v>
       </c>
       <c r="B787" t="n">
-        <v>0.07315491568997977</v>
+        <v>0.07315491568997978</v>
       </c>
       <c r="C787" t="n">
         <v>0.0650532001340416</v>
@@ -13830,7 +13830,7 @@
         <v>0.07298896391488092</v>
       </c>
       <c r="C789" t="n">
-        <v>0.06490824065481773</v>
+        <v>0.06490824065481772</v>
       </c>
       <c r="D789" t="n">
         <v>0.9741080530071355</v>
@@ -13864,7 +13864,7 @@
         <v>0.07282373834967264</v>
       </c>
       <c r="C791" t="n">
-        <v>0.0647639915302778</v>
+        <v>0.06476399153027783</v>
       </c>
       <c r="D791" t="n">
         <v>0.9743119266055046</v>
@@ -13946,7 +13946,7 @@
         <v>795</v>
       </c>
       <c r="B796" t="n">
-        <v>0.07241381537817827</v>
+        <v>0.07241381537817829</v>
       </c>
       <c r="C796" t="n">
         <v>0.06440643853824189</v>
@@ -13966,7 +13966,7 @@
         <v>0.07233236379440264</v>
       </c>
       <c r="C797" t="n">
-        <v>0.06433544849462852</v>
+        <v>0.06433544849462851</v>
       </c>
       <c r="D797" t="n">
         <v>0.9745158002038736</v>
@@ -14014,7 +14014,7 @@
         <v>799</v>
       </c>
       <c r="B800" t="n">
-        <v>0.07208906303525711</v>
+        <v>0.07208906303525713</v>
       </c>
       <c r="C800" t="n">
         <v>0.06412350686189039</v>
@@ -14034,7 +14034,7 @@
         <v>0.07200831191907335</v>
       </c>
       <c r="C801" t="n">
-        <v>0.0640532001835251</v>
+        <v>0.06405320018352509</v>
       </c>
       <c r="D801" t="n">
         <v>0.9747196738022426</v>
@@ -14051,7 +14051,7 @@
         <v>0.07192773428435381</v>
       </c>
       <c r="C802" t="n">
-        <v>0.06398306263178183</v>
+        <v>0.06398306263178184</v>
       </c>
       <c r="D802" t="n">
         <v>0.9747196738022426</v>
@@ -14068,7 +14068,7 @@
         <v>0.07184732948483979</v>
       </c>
       <c r="C803" t="n">
-        <v>0.06391309352906176</v>
+        <v>0.06391309352906174</v>
       </c>
       <c r="D803" t="n">
         <v>0.9747196738022426</v>
@@ -14102,7 +14102,7 @@
         <v>0.0716870358259237</v>
       </c>
       <c r="C805" t="n">
-        <v>0.06377365798069877</v>
+        <v>0.06377365798069876</v>
       </c>
       <c r="D805" t="n">
         <v>0.9747196738022426</v>
@@ -14116,7 +14116,7 @@
         <v>805</v>
       </c>
       <c r="B806" t="n">
-        <v>0.07160714569345693</v>
+        <v>0.07160714569345691</v>
       </c>
       <c r="C806" t="n">
         <v>0.06370419020017346</v>
@@ -14153,7 +14153,7 @@
         <v>0.07144787566863768</v>
       </c>
       <c r="C808" t="n">
-        <v>0.06356575131926559</v>
+        <v>0.06356575131926558</v>
       </c>
       <c r="D808" t="n">
         <v>0.9747196738022426</v>
@@ -14187,7 +14187,7 @@
         <v>0.07128928180313054</v>
       </c>
       <c r="C810" t="n">
-        <v>0.06342797031517554</v>
+        <v>0.06342797031517551</v>
       </c>
       <c r="D810" t="n">
         <v>0.9751274209989806</v>
@@ -14204,7 +14204,7 @@
         <v>0.07121023688389862</v>
       </c>
       <c r="C811" t="n">
-        <v>0.06335932489534779</v>
+        <v>0.0633593248953478</v>
       </c>
       <c r="D811" t="n">
         <v>0.9751274209989806</v>
@@ -14221,7 +14221,7 @@
         <v>0.07113135915647818</v>
       </c>
       <c r="C812" t="n">
-        <v>0.0632908420065653</v>
+        <v>0.06329084200656532</v>
       </c>
       <c r="D812" t="n">
         <v>0.9753312945973497</v>
@@ -14269,7 +14269,7 @@
         <v>814</v>
       </c>
       <c r="B815" t="n">
-        <v>0.07089572306046425</v>
+        <v>0.07089572306046427</v>
       </c>
       <c r="C815" t="n">
         <v>0.06308636216516178</v>
@@ -14303,7 +14303,7 @@
         <v>816</v>
       </c>
       <c r="B817" t="n">
-        <v>0.07073945723401537</v>
+        <v>0.07073945723401538</v>
       </c>
       <c r="C817" t="n">
         <v>0.06295084332973977</v>
@@ -14357,7 +14357,7 @@
         <v>0.0705062840102426</v>
       </c>
       <c r="C820" t="n">
-        <v>0.06274875424174808</v>
+        <v>0.0627487542417481</v>
       </c>
       <c r="D820" t="n">
         <v>0.9759429153924567</v>
@@ -14371,7 +14371,7 @@
         <v>820</v>
       </c>
       <c r="B821" t="n">
-        <v>0.07042888407035319</v>
+        <v>0.07042888407035322</v>
       </c>
       <c r="C821" t="n">
         <v>0.06268170587149766</v>
@@ -14422,10 +14422,10 @@
         <v>823</v>
       </c>
       <c r="B824" t="n">
-        <v>0.07019764958792063</v>
+        <v>0.07019764958792064</v>
       </c>
       <c r="C824" t="n">
-        <v>0.06248149627081388</v>
+        <v>0.06248149627081387</v>
       </c>
       <c r="D824" t="n">
         <v>0.9759429153924567</v>
@@ -14490,7 +14490,7 @@
         <v>827</v>
       </c>
       <c r="B828" t="n">
-        <v>0.06989156823857838</v>
+        <v>0.06989156823857841</v>
       </c>
       <c r="C828" t="n">
         <v>0.06221671077731058</v>
@@ -14541,7 +14541,7 @@
         <v>830</v>
       </c>
       <c r="B831" t="n">
-        <v>0.06966366118385764</v>
+        <v>0.06966366118385765</v>
       </c>
       <c r="C831" t="n">
         <v>0.06201972164365188</v>
@@ -14561,7 +14561,7 @@
         <v>0.06958800428027916</v>
       </c>
       <c r="C832" t="n">
-        <v>0.06195436028545278</v>
+        <v>0.06195436028545279</v>
       </c>
       <c r="D832" t="n">
         <v>0.9761467889908257</v>
@@ -14575,7 +14575,7 @@
         <v>832</v>
       </c>
       <c r="B833" t="n">
-        <v>0.06951250253226031</v>
+        <v>0.06951250253226032</v>
       </c>
       <c r="C833" t="n">
         <v>0.06188914882267128</v>
@@ -14592,7 +14592,7 @@
         <v>833</v>
       </c>
       <c r="B834" t="n">
-        <v>0.06943715540356911</v>
+        <v>0.06943715540356912</v>
       </c>
       <c r="C834" t="n">
         <v>0.0618240866915965</v>
@@ -14609,10 +14609,10 @@
         <v>834</v>
       </c>
       <c r="B835" t="n">
-        <v>0.06936196236116475</v>
+        <v>0.06936196236116476</v>
       </c>
       <c r="C835" t="n">
-        <v>0.06175917333178041</v>
+        <v>0.0617591733317804</v>
       </c>
       <c r="D835" t="n">
         <v>0.9763506625891947</v>
@@ -14694,7 +14694,7 @@
         <v>839</v>
       </c>
       <c r="B840" t="n">
-        <v>0.06898829000780211</v>
+        <v>0.0689882900078021</v>
       </c>
       <c r="C840" t="n">
         <v>0.06143681871128907</v>
@@ -14711,10 +14711,10 @@
         <v>840</v>
       </c>
       <c r="B841" t="n">
-        <v>0.06891401046537482</v>
+        <v>0.06891401046537483</v>
       </c>
       <c r="C841" t="n">
-        <v>0.06137278638933433</v>
+        <v>0.06137278638933434</v>
       </c>
       <c r="D841" t="n">
         <v>0.9765545361875637</v>
@@ -14731,7 +14731,7 @@
         <v>0.06883988136557799</v>
       </c>
       <c r="C842" t="n">
-        <v>0.06130889900486788</v>
+        <v>0.06130889900486789</v>
       </c>
       <c r="D842" t="n">
         <v>0.9765545361875637</v>
@@ -14748,7 +14748,7 @@
         <v>0.06876590220016505</v>
       </c>
       <c r="C843" t="n">
-        <v>0.06124515602269467</v>
+        <v>0.06124515602269468</v>
       </c>
       <c r="D843" t="n">
         <v>0.9765545361875637</v>
@@ -14813,10 +14813,10 @@
         <v>846</v>
       </c>
       <c r="B847" t="n">
-        <v>0.0684714748223324</v>
+        <v>0.06847147482233241</v>
       </c>
       <c r="C847" t="n">
-        <v>0.06099161751939886</v>
+        <v>0.06099161751939887</v>
       </c>
       <c r="D847" t="n">
         <v>0.9765545361875637</v>
@@ -14830,7 +14830,7 @@
         <v>847</v>
       </c>
       <c r="B848" t="n">
-        <v>0.0683982378097783</v>
+        <v>0.06839823780977831</v>
       </c>
       <c r="C848" t="n">
         <v>0.06092858862681665</v>
@@ -14847,10 +14847,10 @@
         <v>848</v>
       </c>
       <c r="B849" t="n">
-        <v>0.06832514774463892</v>
+        <v>0.06832514774463894</v>
       </c>
       <c r="C849" t="n">
-        <v>0.06086570098867357</v>
+        <v>0.06086570098867358</v>
       </c>
       <c r="D849" t="n">
         <v>0.9765545361875637</v>
@@ -14864,7 +14864,7 @@
         <v>849</v>
       </c>
       <c r="B850" t="n">
-        <v>0.0682522041393237</v>
+        <v>0.06825220413932372</v>
       </c>
       <c r="C850" t="n">
         <v>0.06080295409067159</v>
@@ -14884,7 +14884,7 @@
         <v>0.06817940650911619</v>
       </c>
       <c r="C851" t="n">
-        <v>0.0607403474214095</v>
+        <v>0.06074034742140949</v>
       </c>
       <c r="D851" t="n">
         <v>0.9765545361875637</v>
@@ -14901,7 +14901,7 @@
         <v>0.06810675437215509</v>
       </c>
       <c r="C852" t="n">
-        <v>0.06067788047236099</v>
+        <v>0.060677880472361</v>
       </c>
       <c r="D852" t="n">
         <v>0.9765545361875637</v>
@@ -14932,10 +14932,10 @@
         <v>853</v>
       </c>
       <c r="B854" t="n">
-        <v>0.06796188466469019</v>
+        <v>0.06796188466469021</v>
       </c>
       <c r="C854" t="n">
-        <v>0.06055336371504522</v>
+        <v>0.06055336371504523</v>
       </c>
       <c r="D854" t="n">
         <v>0.9765545361875637</v>
@@ -14952,7 +14952,7 @@
         <v>0.06788966614457108</v>
       </c>
       <c r="C855" t="n">
-        <v>0.06049131290390649</v>
+        <v>0.0604913129039065</v>
       </c>
       <c r="D855" t="n">
         <v>0.9765545361875637</v>
@@ -14986,7 +14986,7 @@
         <v>0.06774565941840351</v>
       </c>
       <c r="C857" t="n">
-        <v>0.06036762393044001</v>
+        <v>0.06036762393043999</v>
       </c>
       <c r="D857" t="n">
         <v>0.9765545361875637</v>
@@ -15037,7 +15037,7 @@
         <v>0.06753071813739694</v>
       </c>
       <c r="C860" t="n">
-        <v>0.06018311471625227</v>
+        <v>0.06018311471625226</v>
       </c>
       <c r="D860" t="n">
         <v>0.9765545361875637</v>
@@ -15088,7 +15088,7 @@
         <v>0.06731704840959576</v>
       </c>
       <c r="C863" t="n">
-        <v>0.05999982294197582</v>
+        <v>0.05999982294197581</v>
       </c>
       <c r="D863" t="n">
         <v>0.9767584097859328</v>
@@ -15122,7 +15122,7 @@
         <v>0.06717530231151003</v>
       </c>
       <c r="C865" t="n">
-        <v>0.05987829839494066</v>
+        <v>0.05987829839494065</v>
       </c>
       <c r="D865" t="n">
         <v>0.9769622833843017</v>
@@ -15136,10 +15136,10 @@
         <v>865</v>
       </c>
       <c r="B866" t="n">
-        <v>0.06710463803931935</v>
+        <v>0.06710463803931933</v>
       </c>
       <c r="C866" t="n">
-        <v>0.05981773569291919</v>
+        <v>0.05981773569291921</v>
       </c>
       <c r="D866" t="n">
         <v>0.9769622833843017</v>
@@ -15153,10 +15153,10 @@
         <v>866</v>
       </c>
       <c r="B867" t="n">
-        <v>0.0670341123625194</v>
+        <v>0.06703411236251941</v>
       </c>
       <c r="C867" t="n">
-        <v>0.05975730541380291</v>
+        <v>0.05975730541380292</v>
       </c>
       <c r="D867" t="n">
         <v>0.9771661569826707</v>
@@ -15204,7 +15204,7 @@
         <v>869</v>
       </c>
       <c r="B870" t="n">
-        <v>0.06682336253046435</v>
+        <v>0.06682336253046434</v>
       </c>
       <c r="C870" t="n">
         <v>0.05957680447263328</v>
@@ -15241,7 +15241,7 @@
         <v>0.0666835476446646</v>
       </c>
       <c r="C872" t="n">
-        <v>0.05945712416123819</v>
+        <v>0.0594571241612382</v>
       </c>
       <c r="D872" t="n">
         <v>0.9771661569826707</v>
@@ -15258,7 +15258,7 @@
         <v>0.06661384441666046</v>
       </c>
       <c r="C873" t="n">
-        <v>0.05939747873410905</v>
+        <v>0.05939747873410907</v>
       </c>
       <c r="D873" t="n">
         <v>0.9771661569826707</v>
@@ -15272,7 +15272,7 @@
         <v>873</v>
       </c>
       <c r="B874" t="n">
-        <v>0.06654427676624024</v>
+        <v>0.06654427676624025</v>
       </c>
       <c r="C874" t="n">
         <v>0.05933796252450244</v>
@@ -15289,10 +15289,10 @@
         <v>874</v>
       </c>
       <c r="B875" t="n">
-        <v>0.06647484427220407</v>
+        <v>0.06647484427220406</v>
       </c>
       <c r="C875" t="n">
-        <v>0.05927857508429007</v>
+        <v>0.05927857508429006</v>
       </c>
       <c r="D875" t="n">
         <v>0.9771661569826707</v>
@@ -15306,10 +15306,10 @@
         <v>875</v>
       </c>
       <c r="B876" t="n">
-        <v>0.06640554651577973</v>
+        <v>0.06640554651577972</v>
       </c>
       <c r="C876" t="n">
-        <v>0.05921931596773215</v>
+        <v>0.05921931596773213</v>
       </c>
       <c r="D876" t="n">
         <v>0.9773700305810398</v>
@@ -15323,7 +15323,7 @@
         <v>876</v>
       </c>
       <c r="B877" t="n">
-        <v>0.06633638308060578</v>
+        <v>0.06633638308060577</v>
       </c>
       <c r="C877" t="n">
         <v>0.05916018473145839</v>
@@ -15343,7 +15343,7 @@
         <v>0.06626735355271479</v>
       </c>
       <c r="C878" t="n">
-        <v>0.05910118093444939</v>
+        <v>0.05910118093444938</v>
       </c>
       <c r="D878" t="n">
         <v>0.9773700305810398</v>
@@ -15394,7 +15394,7 @@
         <v>0.06606106430862241</v>
       </c>
       <c r="C881" t="n">
-        <v>0.05892492980368678</v>
+        <v>0.05892492980368679</v>
       </c>
       <c r="D881" t="n">
         <v>0.9773700305810398</v>
@@ -15425,10 +15425,10 @@
         <v>882</v>
       </c>
       <c r="B883" t="n">
-        <v>0.06592420019911172</v>
+        <v>0.0659242001991117</v>
       </c>
       <c r="C883" t="n">
-        <v>0.05880805826490654</v>
+        <v>0.05880805826490656</v>
       </c>
       <c r="D883" t="n">
         <v>0.9773700305810398</v>
@@ -15445,7 +15445,7 @@
         <v>0.06585596555355777</v>
       </c>
       <c r="C884" t="n">
-        <v>0.0587498099713829</v>
+        <v>0.05874980997138292</v>
       </c>
       <c r="D884" t="n">
         <v>0.9773700305810398</v>
@@ -15476,7 +15476,7 @@
         <v>885</v>
       </c>
       <c r="B886" t="n">
-        <v>0.06571988909245639</v>
+        <v>0.06571988909245641</v>
       </c>
       <c r="C886" t="n">
         <v>0.05863368621064708</v>
@@ -15561,10 +15561,10 @@
         <v>890</v>
       </c>
       <c r="B891" t="n">
-        <v>0.06538197115164739</v>
+        <v>0.06538197115164737</v>
       </c>
       <c r="C891" t="n">
-        <v>0.05834553204679966</v>
+        <v>0.05834553204679967</v>
       </c>
       <c r="D891" t="n">
         <v>0.9777777777777777</v>
@@ -15578,10 +15578,10 @@
         <v>891</v>
       </c>
       <c r="B892" t="n">
-        <v>0.06531477416020227</v>
+        <v>0.06531477416020229</v>
       </c>
       <c r="C892" t="n">
-        <v>0.05828826736511914</v>
+        <v>0.05828826736511915</v>
       </c>
       <c r="D892" t="n">
         <v>0.9777777777777777</v>
@@ -15615,7 +15615,7 @@
         <v>0.06518076372075032</v>
       </c>
       <c r="C894" t="n">
-        <v>0.05817410087675449</v>
+        <v>0.0581741008767545</v>
       </c>
       <c r="D894" t="n">
         <v>0.9777777777777777</v>
@@ -15632,7 +15632,7 @@
         <v>0.06511394951904861</v>
       </c>
       <c r="C895" t="n">
-        <v>0.05811719826036913</v>
+        <v>0.05811719826036912</v>
       </c>
       <c r="D895" t="n">
         <v>0.9777777777777777</v>
@@ -15680,10 +15680,10 @@
         <v>897</v>
       </c>
       <c r="B898" t="n">
-        <v>0.06491426650798572</v>
+        <v>0.06491426650798574</v>
       </c>
       <c r="C898" t="n">
-        <v>0.05794720810683828</v>
+        <v>0.05794720810683829</v>
       </c>
       <c r="D898" t="n">
         <v>0.9777777777777777</v>
@@ -15700,7 +15700,7 @@
         <v>0.06484795747051472</v>
       </c>
       <c r="C899" t="n">
-        <v>0.05789078262823628</v>
+        <v>0.05789078262823627</v>
       </c>
       <c r="D899" t="n">
         <v>0.9777777777777777</v>
@@ -15731,7 +15731,7 @@
         <v>900</v>
       </c>
       <c r="B901" t="n">
-        <v>0.06471571514915701</v>
+        <v>0.06471571514915703</v>
       </c>
       <c r="C901" t="n">
         <v>0.05777828616388149</v>
@@ -15768,7 +15768,7 @@
         <v>0.06458397141978683</v>
       </c>
       <c r="C903" t="n">
-        <v>0.05766625975368139</v>
+        <v>0.05766625975368137</v>
       </c>
       <c r="D903" t="n">
         <v>0.9777777777777777</v>
@@ -15799,7 +15799,7 @@
         <v>904</v>
       </c>
       <c r="B905" t="n">
-        <v>0.06445272341488495</v>
+        <v>0.06445272341488496</v>
       </c>
       <c r="C905" t="n">
         <v>0.05755470030083089</v>
@@ -15819,7 +15819,7 @@
         <v>0.06438728442159881</v>
       </c>
       <c r="C906" t="n">
-        <v>0.05749909472391278</v>
+        <v>0.05749909472391279</v>
       </c>
       <c r="D906" t="n">
         <v>0.9777777777777777</v>
@@ -15853,7 +15853,7 @@
         <v>0.06425677469526972</v>
       </c>
       <c r="C908" t="n">
-        <v>0.05738822996634822</v>
+        <v>0.05738822996634823</v>
       </c>
       <c r="D908" t="n">
         <v>0.9792048929663608</v>
@@ -15870,7 +15870,7 @@
         <v>0.06419170326472515</v>
       </c>
       <c r="C909" t="n">
-        <v>0.05733297003010255</v>
+        <v>0.05733297003010256</v>
       </c>
       <c r="D909" t="n">
         <v>0.9794087665647299</v>
@@ -15887,7 +15887,7 @@
         <v>0.06412675366074215</v>
       </c>
       <c r="C910" t="n">
-        <v>0.05727782455483323</v>
+        <v>0.05727782455483325</v>
       </c>
       <c r="D910" t="n">
         <v>0.9794087665647299</v>
@@ -15921,7 +15921,7 @@
         <v>0.06399721855811581</v>
       </c>
       <c r="C912" t="n">
-        <v>0.05716787549581515</v>
+        <v>0.05716787549581517</v>
       </c>
       <c r="D912" t="n">
         <v>0.9794087665647299</v>
@@ -15938,7 +15938,7 @@
         <v>0.06393263237691786</v>
       </c>
       <c r="C913" t="n">
-        <v>0.05711307117078197</v>
+        <v>0.05711307117078195</v>
       </c>
       <c r="D913" t="n">
         <v>0.9794087665647299</v>
@@ -15952,10 +15952,10 @@
         <v>913</v>
       </c>
       <c r="B914" t="n">
-        <v>0.06386816665714205</v>
+        <v>0.06386816665714208</v>
       </c>
       <c r="C914" t="n">
-        <v>0.05705837982412594</v>
+        <v>0.05705837982412593</v>
       </c>
       <c r="D914" t="n">
         <v>0.9794087665647299</v>
@@ -15969,7 +15969,7 @@
         <v>914</v>
       </c>
       <c r="B915" t="n">
-        <v>0.06380382106206131</v>
+        <v>0.06380382106206132</v>
       </c>
       <c r="C915" t="n">
         <v>0.05700380108955681</v>
@@ -15986,10 +15986,10 @@
         <v>915</v>
       </c>
       <c r="B916" t="n">
-        <v>0.06373959525674158</v>
+        <v>0.0637395952567416</v>
       </c>
       <c r="C916" t="n">
-        <v>0.05694933460249815</v>
+        <v>0.05694933460249817</v>
       </c>
       <c r="D916" t="n">
         <v>0.9794087665647299</v>
@@ -16006,7 +16006,7 @@
         <v>0.06367548890802699</v>
       </c>
       <c r="C917" t="n">
-        <v>0.05689498000007265</v>
+        <v>0.05689498000007266</v>
       </c>
       <c r="D917" t="n">
         <v>0.9794087665647299</v>
@@ -16054,7 +16054,7 @@
         <v>919</v>
       </c>
       <c r="B920" t="n">
-        <v>0.06348388329631562</v>
+        <v>0.06348388329631563</v>
       </c>
       <c r="C920" t="n">
         <v>0.05673258389700209</v>
@@ -16088,10 +16088,10 @@
         <v>921</v>
       </c>
       <c r="B922" t="n">
-        <v>0.06335673747567612</v>
+        <v>0.06335673747567613</v>
       </c>
       <c r="C922" t="n">
-        <v>0.05662487267383798</v>
+        <v>0.05662487267383799</v>
       </c>
       <c r="D922" t="n">
         <v>0.9794087665647299</v>
@@ -16176,7 +16176,7 @@
         <v>0.06304092348160456</v>
       </c>
       <c r="C927" t="n">
-        <v>0.05635750898347344</v>
+        <v>0.05635750898347345</v>
       </c>
       <c r="D927" t="n">
         <v>0.9794087665647299</v>
@@ -16190,10 +16190,10 @@
         <v>927</v>
       </c>
       <c r="B928" t="n">
-        <v>0.06297810966100816</v>
+        <v>0.06297810966100817</v>
       </c>
       <c r="C928" t="n">
-        <v>0.0563043616335934</v>
+        <v>0.05630436163359341</v>
       </c>
       <c r="D928" t="n">
         <v>0.9798165137614679</v>
@@ -16207,10 +16207,10 @@
         <v>928</v>
       </c>
       <c r="B929" t="n">
-        <v>0.06291541143247116</v>
+        <v>0.06291541143247115</v>
       </c>
       <c r="C929" t="n">
-        <v>0.05625132194111793</v>
+        <v>0.05625132194111795</v>
       </c>
       <c r="D929" t="n">
         <v>0.9798165137614679</v>
@@ -16227,7 +16227,7 @@
         <v>0.06285282848461569</v>
       </c>
       <c r="C930" t="n">
-        <v>0.05619838956396203</v>
+        <v>0.05619838956396202</v>
       </c>
       <c r="D930" t="n">
         <v>0.9798165137614679</v>
@@ -16261,7 +16261,7 @@
         <v>0.06272800719329326</v>
       </c>
       <c r="C932" t="n">
-        <v>0.05609284539477202</v>
+        <v>0.05609284539477203</v>
       </c>
       <c r="D932" t="n">
         <v>0.9798165137614679</v>
@@ -16278,7 +16278,7 @@
         <v>0.0626657682348829</v>
       </c>
       <c r="C933" t="n">
-        <v>0.05604023292603181</v>
+        <v>0.05604023292603182</v>
       </c>
       <c r="D933" t="n">
         <v>0.9798165137614679</v>
@@ -16292,10 +16292,10 @@
         <v>933</v>
       </c>
       <c r="B934" t="n">
-        <v>0.06260364332723903</v>
+        <v>0.06260364332723901</v>
       </c>
       <c r="C934" t="n">
-        <v>0.05598772641917284</v>
+        <v>0.05598772641917283</v>
       </c>
       <c r="D934" t="n">
         <v>0.9800203873598369</v>
@@ -16309,10 +16309,10 @@
         <v>934</v>
       </c>
       <c r="B935" t="n">
-        <v>0.06254163216671091</v>
+        <v>0.06254163216671092</v>
       </c>
       <c r="C935" t="n">
-        <v>0.05593532553949577</v>
+        <v>0.05593532553949575</v>
       </c>
       <c r="D935" t="n">
         <v>0.9800203873598369</v>
@@ -16394,10 +16394,10 @@
         <v>939</v>
       </c>
       <c r="B940" t="n">
-        <v>0.06223327204746182</v>
+        <v>0.06223327204746183</v>
       </c>
       <c r="C940" t="n">
-        <v>0.05567489393434666</v>
+        <v>0.05567489393434667</v>
       </c>
       <c r="D940" t="n">
         <v>0.9802242609582059</v>
@@ -16414,7 +16414,7 @@
         <v>0.06217193707615527</v>
       </c>
       <c r="C941" t="n">
-        <v>0.0556231198687466</v>
+        <v>0.05562311986874659</v>
       </c>
       <c r="D941" t="n">
         <v>0.9802242609582059</v>
@@ -16428,7 +16428,7 @@
         <v>941</v>
       </c>
       <c r="B942" t="n">
-        <v>0.06211071376771297</v>
+        <v>0.06211071376771295</v>
       </c>
       <c r="C942" t="n">
         <v>0.05557144912700727</v>
@@ -16482,7 +16482,7 @@
         <v>0.06192771090635725</v>
       </c>
       <c r="C945" t="n">
-        <v>0.05541705361623692</v>
+        <v>0.0554170536162369</v>
       </c>
       <c r="D945" t="n">
         <v>0.9802242609582059</v>
@@ -16547,10 +16547,10 @@
         <v>948</v>
       </c>
       <c r="B949" t="n">
-        <v>0.06168525281317083</v>
+        <v>0.06168525281317082</v>
       </c>
       <c r="C949" t="n">
-        <v>0.0552126199929019</v>
+        <v>0.05521261999290188</v>
       </c>
       <c r="D949" t="n">
         <v>0.980428134556575</v>
@@ -16564,7 +16564,7 @@
         <v>949</v>
       </c>
       <c r="B950" t="n">
-        <v>0.06162491241030206</v>
+        <v>0.06162491241030205</v>
       </c>
       <c r="C950" t="n">
         <v>0.05516176430568447</v>
@@ -16581,7 +16581,7 @@
         <v>950</v>
       </c>
       <c r="B951" t="n">
-        <v>0.06156468109113707</v>
+        <v>0.06156468109113708</v>
       </c>
       <c r="C951" t="n">
         <v>0.05511100907772916</v>
@@ -16615,7 +16615,7 @@
         <v>952</v>
       </c>
       <c r="B953" t="n">
-        <v>0.06144454458530563</v>
+        <v>0.06144454458530565</v>
       </c>
       <c r="C953" t="n">
         <v>0.05500979875326189</v>
@@ -16632,7 +16632,7 @@
         <v>953</v>
       </c>
       <c r="B954" t="n">
-        <v>0.06138463884249907</v>
+        <v>0.06138463884249905</v>
       </c>
       <c r="C954" t="n">
         <v>0.05495934303666213</v>
@@ -16649,7 +16649,7 @@
         <v>954</v>
       </c>
       <c r="B955" t="n">
-        <v>0.06132484107108985</v>
+        <v>0.06132484107108986</v>
       </c>
       <c r="C955" t="n">
         <v>0.05490898653912732</v>
@@ -16686,7 +16686,7 @@
         <v>0.06120556834383327</v>
       </c>
       <c r="C957" t="n">
-        <v>0.0548085699744144</v>
+        <v>0.05480856997441442</v>
       </c>
       <c r="D957" t="n">
         <v>0.9806320081549439</v>
@@ -16703,7 +16703,7 @@
         <v>0.06114609284170718</v>
       </c>
       <c r="C958" t="n">
-        <v>0.05475850929679474</v>
+        <v>0.05475850929679475</v>
       </c>
       <c r="D958" t="n">
         <v>0.9806320081549439</v>
@@ -16717,10 +16717,10 @@
         <v>958</v>
       </c>
       <c r="B959" t="n">
-        <v>0.0610867242183953</v>
+        <v>0.06108672421839532</v>
       </c>
       <c r="C959" t="n">
-        <v>0.05470854661733637</v>
+        <v>0.05470854661733639</v>
       </c>
       <c r="D959" t="n">
         <v>0.9806320081549439</v>
@@ -16754,7 +16754,7 @@
         <v>0.06096830652874077</v>
       </c>
       <c r="C961" t="n">
-        <v>0.05460891404490042</v>
+        <v>0.0546089140449004</v>
       </c>
       <c r="D961" t="n">
         <v>0.9806320081549439</v>
@@ -16785,10 +16785,10 @@
         <v>962</v>
       </c>
       <c r="B963" t="n">
-        <v>0.0608503131275334</v>
+        <v>0.06085031312753342</v>
       </c>
       <c r="C963" t="n">
-        <v>0.0545096698525843</v>
+        <v>0.05450966985258428</v>
       </c>
       <c r="D963" t="n">
         <v>0.9806320081549439</v>
@@ -16819,7 +16819,7 @@
         <v>964</v>
       </c>
       <c r="B965" t="n">
-        <v>0.06073274188573392</v>
+        <v>0.06073274188573391</v>
       </c>
       <c r="C965" t="n">
         <v>0.05441081165402012</v>
@@ -16924,7 +16924,7 @@
         <v>0.06038254009251842</v>
       </c>
       <c r="C971" t="n">
-        <v>0.05411652942303004</v>
+        <v>0.05411652942303001</v>
       </c>
       <c r="D971" t="n">
         <v>0.9808358817533129</v>
@@ -16938,7 +16938,7 @@
         <v>971</v>
       </c>
       <c r="B972" t="n">
-        <v>0.06032453672209308</v>
+        <v>0.06032453672209306</v>
       </c>
       <c r="C972" t="n">
         <v>0.05406781362179296</v>
@@ -16958,7 +16958,7 @@
         <v>0.06026663655006322</v>
       </c>
       <c r="C973" t="n">
-        <v>0.05401919168820471</v>
+        <v>0.05401919168820472</v>
       </c>
       <c r="D973" t="n">
         <v>0.9808358817533129</v>
@@ -17040,7 +17040,7 @@
         <v>977</v>
       </c>
       <c r="B978" t="n">
-        <v>0.05997867477831861</v>
+        <v>0.05997867477831862</v>
       </c>
       <c r="C978" t="n">
         <v>0.0537774800259521</v>
@@ -17057,7 +17057,7 @@
         <v>978</v>
       </c>
       <c r="B979" t="n">
-        <v>0.0599213884778671</v>
+        <v>0.05992138847786711</v>
       </c>
       <c r="C979" t="n">
         <v>0.05372941530699678</v>
@@ -17111,7 +17111,7 @@
         <v>0.05975013719184123</v>
       </c>
       <c r="C982" t="n">
-        <v>0.05358577131076719</v>
+        <v>0.05358577131076721</v>
       </c>
       <c r="D982" t="n">
         <v>0.981243628950051</v>
@@ -17125,7 +17125,7 @@
         <v>982</v>
       </c>
       <c r="B983" t="n">
-        <v>0.05969325514408983</v>
+        <v>0.05969325514408984</v>
       </c>
       <c r="C983" t="n">
         <v>0.05353807243549293</v>
@@ -17193,7 +17193,7 @@
         <v>986</v>
       </c>
       <c r="B987" t="n">
-        <v>0.05946672898484885</v>
+        <v>0.05946672898484887</v>
       </c>
       <c r="C987" t="n">
         <v>0.05334818183509301</v>
@@ -17213,7 +17213,7 @@
         <v>0.05941034673669399</v>
       </c>
       <c r="C988" t="n">
-        <v>0.05330093403637268</v>
+        <v>0.0533009340363727</v>
       </c>
       <c r="D988" t="n">
         <v>0.981243628950051</v>
@@ -17230,7 +17230,7 @@
         <v>0.05935406372168432</v>
       </c>
       <c r="C989" t="n">
-        <v>0.0532537756319264</v>
+        <v>0.05325377563192642</v>
       </c>
       <c r="D989" t="n">
         <v>0.981243628950051</v>
@@ -17244,10 +17244,10 @@
         <v>989</v>
       </c>
       <c r="B990" t="n">
-        <v>0.05929787969953065</v>
+        <v>0.05929787969953066</v>
       </c>
       <c r="C990" t="n">
-        <v>0.05320670635021561</v>
+        <v>0.0532067063502156</v>
       </c>
       <c r="D990" t="n">
         <v>0.981243628950051</v>
@@ -17295,7 +17295,7 @@
         <v>992</v>
       </c>
       <c r="B993" t="n">
-        <v>0.05912991919959692</v>
+        <v>0.05912991919959693</v>
       </c>
       <c r="C993" t="n">
         <v>0.05306603053962255</v>
@@ -17349,7 +17349,7 @@
         <v>0.05896284106280158</v>
       </c>
       <c r="C996" t="n">
-        <v>0.05292614714423853</v>
+        <v>0.05292614714423852</v>
       </c>
       <c r="D996" t="n">
         <v>0.981243628950051</v>
@@ -17383,7 +17383,7 @@
         <v>0.05885194269730596</v>
       </c>
       <c r="C998" t="n">
-        <v>0.05283332822547565</v>
+        <v>0.05283332822547566</v>
       </c>
       <c r="D998" t="n">
         <v>0.981243628950051</v>
@@ -17400,7 +17400,7 @@
         <v>0.05879663893029602</v>
       </c>
       <c r="C999" t="n">
-        <v>0.05278704897605607</v>
+        <v>0.05278704897605609</v>
       </c>
       <c r="D999" t="n">
         <v>0.981243628950051</v>
